--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1485851.0</t>
+          <t>1428944.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2357132.54</t>
+          <t>2349514.76</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-124030.49</v>
+        <v>-130000.86</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>66.006</t>
+          <t>74.073</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1559706.4</t>
+          <t>1485851.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1953878.1</t>
+          <t>1868651.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2371167.86</t>
+          <t>2357132.54</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-394171</t>
+          <t>-382800</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-89111.03010474489</t>
+          <t>-94483.25454918241</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-142764.16</v>
+        <v>-124030.49</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-34.05</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,27 +1608,27 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.176</t>
+          <t>66.006</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-20.17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.82</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.45</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>485673.0</t>
+          <t>1514150.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1707269.8</t>
+          <t>1559706.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1978571.1</t>
+          <t>1953878.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2372228.6</t>
+          <t>2371167.86</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-271301</t>
+          <t>-394171</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-79355.91633946935</t>
+          <t>-89111.03010474489</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-145626.5</v>
+        <v>-142764.16</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-34.05</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,27 +2039,27 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>89.795</t>
+          <t>21.176</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-29.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>65.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>23.02</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>23.01</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.18</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.68</t>
+          <t>-104.45</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2061436.0</t>
+          <t>485673.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1902325.8</t>
+          <t>1707269.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2069268.0</t>
+          <t>1978571.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2377009.5</t>
+          <t>2372228.6</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-166942</t>
+          <t>-271301</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-67306.72009094176</t>
+          <t>-79355.91633946935</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-34320.64</v>
+        <v>-145626.5</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>72.437</t>
+          <t>89.795</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.59</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-104.68</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1678367.0</t>
+          <t>2061436.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2127476.0</t>
+          <t>1902325.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2027376.4</t>
+          <t>2069268.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2400065.28</t>
+          <t>2377009.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>100099</t>
+          <t>-166942</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-73304.18881022699</t>
+          <t>-67306.72009094176</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-42918.29</v>
+        <v>-34320.64</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-33.48</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,27 +2901,27 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>89.409</t>
+          <t>72.437</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.51</t>
+          <t>-28.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.19</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2058906.0</t>
+          <t>1678367.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2251451.0</t>
+          <t>2127476.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2030675.9</t>
+          <t>2027376.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2410232.12</t>
+          <t>2400065.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>220775</t>
+          <t>100099</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-78828.89719921869</t>
+          <t>-73304.18881022699</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-12624.75</v>
+        <v>-42918.29</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-34.33</t>
+          <t>-33.48</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>98.245</t>
+          <t>89.409</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-29.51</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>23.14</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-105.19</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2251967.0</t>
+          <t>2058906.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2348049.8</t>
+          <t>2251451.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2024201.0</t>
+          <t>2030675.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2424454.06</t>
+          <t>2410232.12</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>323848</t>
+          <t>220775</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-90866.01536825285</t>
+          <t>-78828.89719921869</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-9669.41</v>
+        <v>-12624.75</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-34.33</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>63.956</t>
+          <t>98.245</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14.18</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>61.67</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.52</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1460953.0</t>
+          <t>2251967.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2249872.4</t>
+          <t>2348049.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1970450.2</t>
+          <t>2024201.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2406507.48</t>
+          <t>2424454.06</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>279422</t>
+          <t>323848</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-105629.0353038595</t>
+          <t>-90866.01536825285</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-25787.26</v>
+        <v>-9669.41</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>138.467</t>
+          <t>63.956</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.05</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>61.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.63</t>
+          <t>-105.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3187187.0</t>
+          <t>1460953.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2236210.2</t>
+          <t>2249872.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2043947.9</t>
+          <t>1970450.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2412556.4</t>
+          <t>2406507.48</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>192262</t>
+          <t>279422</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-120145.7216407908</t>
+          <t>-105629.0353038595</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>36859.71</v>
+        <v>-25787.26</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-33.90</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,37 +4625,37 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>100.474</t>
+          <t>138.467</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.05</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,275 +4888,275 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>22.86</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>24.55</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>5.82</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-105.63</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>19662446.52894356</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>3187187.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>2236210.2</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>2043947.9</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>2412556.4</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>192262</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-120145.7216407908</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>36859.71</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>35.1</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/05/13</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-33.90</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>翔耀</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>翔耀</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>43.84457236842105</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-5.673146924798447</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>22.79115323200866</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>26.31%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>-28.64%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>80.31</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>光學面板,彩色濾光片基板89.00%、其他11.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>翔耀-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>光電業右下上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>24.61</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>25.52</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>10.33</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-105.72</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>19687912.75652174</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>2298242.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1927276.8</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>1901014.4</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2398698.06</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>26262</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-148692.1630994882</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-59914.69</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/05/13</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-35.61</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>翔耀</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>翔耀</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-38.5462828743011</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-22.53113008066411</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>35.45425912147203</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>26.31%</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>-28.64%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>79.43</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>1378</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>光學面板,彩色濾光片基板89.00%、其他11.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>翔耀-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>光電業右下上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>111.672</t>
+          <t>100.474</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,42 +5319,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>25.79</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5364,27 +5364,27 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.61</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-105.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19687912.75652174</t>
+          <t>19662446.52894356</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2541900.0</t>
+          <t>2298242.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1809900.8</t>
+          <t>1927276.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1795473.7</t>
+          <t>1901014.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2415974.7</t>
+          <t>2398698.06</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>26262</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-164833.5222709956</t>
+          <t>-148692.1630994882</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-100779.9</v>
+        <v>-59914.69</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-38.5462828743011</t>
+          <t>43.84457236842105</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-22.53113008066411</t>
+          <t>-5.673146924798447</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>35.45425912147203</t>
+          <t>22.79115323200866</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>80.31</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>30395369.2</t>
+          <t>32593060.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>82590132.42</t>
+          <t>81339733.32</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-6401386.67</v>
+        <v>-4991945.43</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,27 +5918,27 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5968,22 +5968,22 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,27 +6003,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>812.259</t>
+          <t>1046.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-20.30</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-134.40</t>
+          <t>-136.54</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29213195.6</t>
+          <t>30395369.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>34657603.3</t>
+          <t>33994550.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>85238942.98</t>
+          <t>82590132.42</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-5444407</t>
+          <t>-3599181</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-7526874.548620233</t>
+          <t>-7353722.566559221</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-7455976.79</v>
+        <v>-6401386.67</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,22 +6349,22 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6399,22 +6399,22 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,27 +6434,27 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>766.535</t>
+          <t>812.259</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-28.17</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-9.89</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-20.30</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-132.65</t>
+          <t>-134.40</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>28359284.0</t>
+          <t>29564911.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28928388.6</t>
+          <t>29213195.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>40272785.3</t>
+          <t>34657603.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>88728235.7</t>
+          <t>85238942.98</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-11344396</t>
+          <t>-5444407</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-7539765.049814414</t>
+          <t>-7526874.548620233</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-7906141.37</v>
+        <v>-7455976.79</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,37 +6780,37 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6830,22 +6830,22 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,27 +6865,27 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>665.622</t>
+          <t>766.535</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-26.13</t>
+          <t>-28.17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-130.65</t>
+          <t>-132.65</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>24346693.0</t>
+          <t>28359284.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31239206.4</t>
+          <t>28928388.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>42288298.0</t>
+          <t>40272785.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>92652071.9</t>
+          <t>88728235.7</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-11049091</t>
+          <t>-11344396</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-7473151.172777075</t>
+          <t>-7539765.049814414</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-8137697.12</v>
+        <v>-7906141.37</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,37 +7211,37 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,22 +7261,22 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,27 +7296,27 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>917.014</t>
+          <t>665.622</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-19.97</t>
+          <t>-26.13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,67 +7474,67 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>39.79</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-54.61</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-127.63</t>
+          <t>-130.65</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>32766707.0</t>
+          <t>24346693.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>35998408.4</t>
+          <t>31239206.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>44979527.8</t>
+          <t>42288298.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>112767245.36</t>
+          <t>92652071.9</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-8981119</t>
+          <t>-11049091</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-7352324.637023974</t>
+          <t>-7473151.172777075</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-7747938.54</v>
+        <v>-8137697.12</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,27 +7642,27 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7692,22 +7692,22 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,27 +7727,27 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>871.406</t>
+          <t>917.014</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-30.16</t>
+          <t>-19.97</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-70.88</t>
+          <t>-54.61</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-123.86</t>
+          <t>-127.63</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>31028383.0</t>
+          <t>32766707.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>37593731.4</t>
+          <t>35998408.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>53830704.2</t>
+          <t>44979527.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>120062941.96</t>
+          <t>112767245.36</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-16236972</t>
+          <t>-8981119</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-7280394.836870603</t>
+          <t>-7352324.637023974</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-7816572.83</v>
+        <v>-7747938.54</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,27 +8073,27 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8123,22 +8123,22 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,27 +8158,27 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>769.944</t>
+          <t>871.406</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-28.54</t>
+          <t>-30.16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.60</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,87 +8336,87 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-5.55</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-3.49</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>36.5</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>40.04</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>37.81</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-70.88</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-4.71</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>6.33</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>37.05</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>38.88</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>37.71</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-82.93</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-119.63</t>
+          <t>-123.86</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>28140876.0</t>
+          <t>31028383.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>40102011.0</t>
+          <t>37593731.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>56116242.6</t>
+          <t>53830704.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>122048686.88</t>
+          <t>120062941.96</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-16014231</t>
+          <t>-16236972</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-7182907.928896697</t>
+          <t>-7280394.836870603</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-7449209.51</v>
+        <v>-7816572.83</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,27 +8504,27 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8554,22 +8554,22 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,27 +8589,27 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1111.919</t>
+          <t>769.944</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-28.54</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-11.60</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-100.39</t>
+          <t>-82.93</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.56</t>
+          <t>-119.63</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>39913373.0</t>
+          <t>28140876.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>51617182.0</t>
+          <t>40102011.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>60219637.4</t>
+          <t>56116242.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>123707087.1</t>
+          <t>122048686.88</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-8602455</t>
+          <t>-16014231</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-7134489.460488213</t>
+          <t>-7182907.928896697</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-6348985.81</v>
+        <v>-7449209.51</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,27 +8935,27 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8985,22 +8985,22 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,27 +9020,27 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1297.036</t>
+          <t>1111.919</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>37.41</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-108.05</t>
+          <t>-100.39</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.65</t>
+          <t>-115.56</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>48142703.0</t>
+          <t>39913373.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>53337389.6</t>
+          <t>51617182.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>60638983.0</t>
+          <t>60219637.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>126346717.8</t>
+          <t>123707087.1</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-7301593</t>
+          <t>-8602455</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-7277308.306450214</t>
+          <t>-7134489.460488213</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-5811827.14</v>
+        <v>-6348985.81</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>16.40</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,37 +9366,37 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9416,22 +9416,22 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,27 +9451,27 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1063.249</t>
+          <t>1297.036</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-8.56</t>
+          <t>-12.04</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>40.21</t>
+          <t>40.17</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-100.33</t>
+          <t>-108.05</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-108.51</t>
+          <t>-111.65</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>40743322.0</t>
+          <t>48142703.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>53960647.2</t>
+          <t>53337389.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>59011448.7</t>
+          <t>60638983.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>131969749.54</t>
+          <t>126346717.8</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-5050801</t>
+          <t>-7301593</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-7543759.427688057</t>
+          <t>-7277308.306450214</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-5718606.29</v>
+        <v>-5811827.14</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>16.40</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,22 +9797,22 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9847,22 +9847,22 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,27 +9882,27 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1142.856</t>
+          <t>1063.249</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>-8.56</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,32 +10080,32 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>39.06</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-113.04</t>
+          <t>-100.33</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.37</t>
+          <t>-108.51</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>246842825.1577424</t>
+          <t>246580960.8815029</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>43569781.0</t>
+          <t>40743322.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>70067677.0</t>
+          <t>53960647.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>59205895.9</t>
+          <t>59011448.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>135177069.3</t>
+          <t>131969749.54</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>10861781</t>
+          <t>-5050801</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7875605.453188929</t>
+          <t>-7543759.427688057</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-4588406.88</v>
+        <v>-5718606.29</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>12.20051451064665</t>
+          <t>2.372433013308771</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-2.641935686302635</t>
+          <t>-31.93695080052008</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-15.19377481596677</t>
+          <t>-18.77148256015754</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10278,22 +10278,22 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>-7.09%</t>
+          <t>-10.75%</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,27 +10313,27 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1044,37 +1044,37 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>22.63</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
           <t>22.83</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>22.91</t>
-        </is>
-      </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1428944.2</t>
+          <t>1610711.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2349514.76</t>
+          <t>2389474.58</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-130000.86</v>
+        <v>-12697.25</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1485851.0</t>
+          <t>1428944.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2357132.54</t>
+          <t>2349514.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-124030.49</v>
+        <v>-130000.86</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>66.006</t>
+          <t>74.073</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1559706.4</t>
+          <t>1485851.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1953878.1</t>
+          <t>1868651.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2371167.86</t>
+          <t>2357132.54</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-394171</t>
+          <t>-382800</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-89111.03010474489</t>
+          <t>-94483.25454918241</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-142764.16</v>
+        <v>-124030.49</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-34.05</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21.176</t>
+          <t>66.006</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-20.17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.82</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.45</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>485673.0</t>
+          <t>1514150.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1707269.8</t>
+          <t>1559706.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1978571.1</t>
+          <t>1953878.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2372228.6</t>
+          <t>2371167.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-271301</t>
+          <t>-394171</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-79355.91633946935</t>
+          <t>-89111.03010474489</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-145626.5</v>
+        <v>-142764.16</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-34.05</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>89.795</t>
+          <t>21.176</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-29.82</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>65.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>23.02</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>23.01</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.18</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.68</t>
+          <t>-104.45</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2061436.0</t>
+          <t>485673.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1902325.8</t>
+          <t>1707269.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2069268.0</t>
+          <t>1978571.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2377009.5</t>
+          <t>2372228.6</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-166942</t>
+          <t>-271301</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-67306.72009094176</t>
+          <t>-79355.91633946935</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-34320.64</v>
+        <v>-145626.5</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>72.437</t>
+          <t>89.795</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.59</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-104.68</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1678367.0</t>
+          <t>2061436.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2127476.0</t>
+          <t>1902325.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2027376.4</t>
+          <t>2069268.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2400065.28</t>
+          <t>2377009.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>100099</t>
+          <t>-166942</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-73304.18881022699</t>
+          <t>-67306.72009094176</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-42918.29</v>
+        <v>-34320.64</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-33.48</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>89.409</t>
+          <t>72.437</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-6.62</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.51</t>
+          <t>-28.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.19</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2058906.0</t>
+          <t>1678367.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2251451.0</t>
+          <t>2127476.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2030675.9</t>
+          <t>2027376.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2410232.12</t>
+          <t>2400065.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>220775</t>
+          <t>100099</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-78828.89719921869</t>
+          <t>-73304.18881022699</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-12624.75</v>
+        <v>-42918.29</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-34.33</t>
+          <t>-33.48</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>98.245</t>
+          <t>89.409</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-29.51</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>23.14</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-105.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2251967.0</t>
+          <t>2058906.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2348049.8</t>
+          <t>2251451.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2024201.0</t>
+          <t>2030675.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2424454.06</t>
+          <t>2410232.12</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>323848</t>
+          <t>220775</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-90866.01536825285</t>
+          <t>-78828.89719921869</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-9669.41</v>
+        <v>-12624.75</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-34.33</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>63.956</t>
+          <t>98.245</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.18</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4462,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>61.67</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.52</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1460953.0</t>
+          <t>2251967.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2249872.4</t>
+          <t>2348049.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1970450.2</t>
+          <t>2024201.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2406507.48</t>
+          <t>2424454.06</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>279422</t>
+          <t>323848</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-105629.0353038595</t>
+          <t>-90866.01536825285</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-25787.26</v>
+        <v>-9669.41</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>138.467</t>
+          <t>63.956</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.05</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>61.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.63</t>
+          <t>-105.52</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19662446.52894356</t>
+          <t>19640471.03757225</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3187187.0</t>
+          <t>1460953.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2236210.2</t>
+          <t>2249872.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2043947.9</t>
+          <t>1970450.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2412556.4</t>
+          <t>2406507.48</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>192262</t>
+          <t>279422</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-120145.7216407908</t>
+          <t>-105629.0353038595</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>36859.71</v>
+        <v>-25787.26</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-33.90</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>80.31</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>100.474</t>
+          <t>138.467</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.05</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,270 +5324,270 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>22.86</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>24.55</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>5.82</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.58</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-105.63</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>19640471.03757225</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>3187187.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>2236210.2</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>2043947.9</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>2412556.4</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>192262</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-120145.7216407908</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>36859.71</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>35.1</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025/05/13</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-33.90</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>翔耀</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>翔耀</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>43.84457236842105</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-5.673146924798447</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>22.79115323200866</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>26.31%</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>-28.64%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>光學面板,彩色濾光片基板89.00%、其他11.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>翔耀-光電業-上市</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>光電業右下上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>24.61</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>25.52</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-2.41</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>10.33</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-105.72</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>19662446.52894356</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>2298242.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1927276.8</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>1901014.4</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2398698.06</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>26262</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-148692.1630994882</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-59914.69</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/05/13</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-35.61</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>翔耀</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>翔耀</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>43.84457236842105</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-5.673146924798447</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>22.79115323200866</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>26.31%</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>-28.64%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>80.31</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>光學面板,彩色濾光片基板89.00%、其他11.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>翔耀-光電業-上市</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>光電業右下上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,64 +5634,64 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-3.26</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>32593060.6</t>
+          <t>36455264.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>81339733.32</t>
+          <t>80453830.28</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-4991945.43</v>
+        <v>-3887846.99</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>30395369.2</t>
+          <t>32593060.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>82590132.42</t>
+          <t>81339733.32</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-6401386.67</v>
+        <v>-4991945.43</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>812.259</t>
+          <t>1046.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-20.30</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-134.40</t>
+          <t>-136.54</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29213195.6</t>
+          <t>30395369.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34657603.3</t>
+          <t>33994550.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>85238942.98</t>
+          <t>82590132.42</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-5444407</t>
+          <t>-3599181</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-7526874.548620233</t>
+          <t>-7353722.566559221</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-7455976.79</v>
+        <v>-6401386.67</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>766.535</t>
+          <t>812.259</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-28.17</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-9.89</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-20.30</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-132.65</t>
+          <t>-134.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>28359284.0</t>
+          <t>29564911.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28928388.6</t>
+          <t>29213195.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40272785.3</t>
+          <t>34657603.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>88728235.7</t>
+          <t>85238942.98</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-11344396</t>
+          <t>-5444407</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-7539765.049814414</t>
+          <t>-7526874.548620233</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-7906141.37</v>
+        <v>-7455976.79</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>665.622</t>
+          <t>766.535</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-26.13</t>
+          <t>-28.17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-130.65</t>
+          <t>-132.65</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>24346693.0</t>
+          <t>28359284.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>31239206.4</t>
+          <t>28928388.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>42288298.0</t>
+          <t>40272785.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>92652071.9</t>
+          <t>88728235.7</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-11049091</t>
+          <t>-11344396</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-7473151.172777075</t>
+          <t>-7539765.049814414</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-8137697.12</v>
+        <v>-7906141.37</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>917.014</t>
+          <t>665.622</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-6.58</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-19.97</t>
+          <t>-26.13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,67 +7905,67 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>39.79</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-54.61</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-127.63</t>
+          <t>-130.65</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>32766707.0</t>
+          <t>24346693.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>35998408.4</t>
+          <t>31239206.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>44979527.8</t>
+          <t>42288298.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>112767245.36</t>
+          <t>92652071.9</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-8981119</t>
+          <t>-11049091</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-7352324.637023974</t>
+          <t>-7473151.172777075</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-7747938.54</v>
+        <v>-8137697.12</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>871.406</t>
+          <t>917.014</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-5.7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-30.16</t>
+          <t>-19.97</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-70.88</t>
+          <t>-54.61</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-123.86</t>
+          <t>-127.63</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31028383.0</t>
+          <t>32766707.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>37593731.4</t>
+          <t>35998408.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>53830704.2</t>
+          <t>44979527.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>120062941.96</t>
+          <t>112767245.36</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-16236972</t>
+          <t>-8981119</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-7280394.836870603</t>
+          <t>-7352324.637023974</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-7816572.83</v>
+        <v>-7747938.54</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>769.944</t>
+          <t>871.406</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-28.54</t>
+          <t>-30.16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.60</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,87 +8767,87 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-5.55</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-3.49</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>36.5</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>40.04</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>37.81</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-70.88</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-4.71</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>6.33</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>37.05</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>38.88</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>37.71</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-82.93</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-119.63</t>
+          <t>-123.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>28140876.0</t>
+          <t>31028383.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>40102011.0</t>
+          <t>37593731.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>56116242.6</t>
+          <t>53830704.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>122048686.88</t>
+          <t>120062941.96</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-16014231</t>
+          <t>-16236972</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-7182907.928896697</t>
+          <t>-7280394.836870603</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-7449209.51</v>
+        <v>-7816572.83</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1111.919</t>
+          <t>769.944</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-28.54</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-11.60</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-100.39</t>
+          <t>-82.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-115.56</t>
+          <t>-119.63</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>39913373.0</t>
+          <t>28140876.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>51617182.0</t>
+          <t>40102011.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>60219637.4</t>
+          <t>56116242.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>123707087.1</t>
+          <t>122048686.88</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-8602455</t>
+          <t>-16014231</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-7134489.460488213</t>
+          <t>-7182907.928896697</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-6348985.81</v>
+        <v>-7449209.51</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1297.036</t>
+          <t>1111.919</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>37.41</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-108.05</t>
+          <t>-100.39</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.65</t>
+          <t>-115.56</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>48142703.0</t>
+          <t>39913373.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>53337389.6</t>
+          <t>51617182.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>60638983.0</t>
+          <t>60219637.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>126346717.8</t>
+          <t>123707087.1</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-7301593</t>
+          <t>-8602455</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-7277308.306450214</t>
+          <t>-7134489.460488213</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-5811827.14</v>
+        <v>-6348985.81</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>16.40</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1063.249</t>
+          <t>1297.036</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-8.56</t>
+          <t>-12.04</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.21</t>
+          <t>40.17</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-100.33</t>
+          <t>-108.05</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-108.51</t>
+          <t>-111.65</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>246580960.8815029</t>
+          <t>246319641.4069264</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>40743322.0</t>
+          <t>48142703.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>53960647.2</t>
+          <t>53337389.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>59011448.7</t>
+          <t>60638983.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>131969749.54</t>
+          <t>126346717.8</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-5050801</t>
+          <t>-7301593</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7543759.427688057</t>
+          <t>-7277308.306450214</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-5718606.29</v>
+        <v>-5811827.14</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>16.40</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,64 +1024,64 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1610711.2</t>
+          <t>1862817.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2389474.58</t>
+          <t>2395938.98</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-12697.25</v>
+        <v>-22072.46</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1475,37 +1475,37 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>22.63</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>22.83</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>22.91</t>
-        </is>
-      </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1428944.2</t>
+          <t>1610711.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2349514.76</t>
+          <t>2389474.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-130000.86</v>
+        <v>-12697.25</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1485851.0</t>
+          <t>1428944.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2357132.54</t>
+          <t>2349514.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-124030.49</v>
+        <v>-130000.86</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>66.006</t>
+          <t>74.073</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1559706.4</t>
+          <t>1485851.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1953878.1</t>
+          <t>1868651.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2371167.86</t>
+          <t>2357132.54</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-394171</t>
+          <t>-382800</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-89111.03010474489</t>
+          <t>-94483.25454918241</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-142764.16</v>
+        <v>-124030.49</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-34.05</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21.176</t>
+          <t>66.006</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-20.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.82</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.45</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>485673.0</t>
+          <t>1514150.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1707269.8</t>
+          <t>1559706.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1978571.1</t>
+          <t>1953878.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2372228.6</t>
+          <t>2371167.86</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-271301</t>
+          <t>-394171</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-79355.91633946935</t>
+          <t>-89111.03010474489</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-145626.5</v>
+        <v>-142764.16</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-34.05</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>89.795</t>
+          <t>21.176</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-29.82</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>65.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>23.02</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>23.01</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.18</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.68</t>
+          <t>-104.45</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2061436.0</t>
+          <t>485673.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1902325.8</t>
+          <t>1707269.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2069268.0</t>
+          <t>1978571.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2377009.5</t>
+          <t>2372228.6</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-166942</t>
+          <t>-271301</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-67306.72009094176</t>
+          <t>-79355.91633946935</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-34320.64</v>
+        <v>-145626.5</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>72.437</t>
+          <t>89.795</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.59</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-104.68</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1678367.0</t>
+          <t>2061436.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2127476.0</t>
+          <t>1902325.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2027376.4</t>
+          <t>2069268.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2400065.28</t>
+          <t>2377009.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>100099</t>
+          <t>-166942</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-73304.18881022699</t>
+          <t>-67306.72009094176</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-42918.29</v>
+        <v>-34320.64</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-33.48</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>89.409</t>
+          <t>72.437</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.51</t>
+          <t>-28.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.19</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2058906.0</t>
+          <t>1678367.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2251451.0</t>
+          <t>2127476.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2030675.9</t>
+          <t>2027376.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2410232.12</t>
+          <t>2400065.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>220775</t>
+          <t>100099</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-78828.89719921869</t>
+          <t>-73304.18881022699</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-12624.75</v>
+        <v>-42918.29</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-34.33</t>
+          <t>-33.48</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>98.245</t>
+          <t>89.409</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-29.51</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4462,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>23.14</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-105.19</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2251967.0</t>
+          <t>2058906.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2348049.8</t>
+          <t>2251451.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2024201.0</t>
+          <t>2030675.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2424454.06</t>
+          <t>2410232.12</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>323848</t>
+          <t>220775</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-90866.01536825285</t>
+          <t>-78828.89719921869</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-9669.41</v>
+        <v>-12624.75</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-34.33</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>63.956</t>
+          <t>98.245</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.18</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>61.67</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.52</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1460953.0</t>
+          <t>2251967.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2249872.4</t>
+          <t>2348049.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1970450.2</t>
+          <t>2024201.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2406507.48</t>
+          <t>2424454.06</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>279422</t>
+          <t>323848</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-105629.0353038595</t>
+          <t>-90866.01536825285</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-25787.26</v>
+        <v>-9669.41</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>138.467</t>
+          <t>63.956</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.05</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>61.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.63</t>
+          <t>-105.52</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19640471.03757225</t>
+          <t>19615909.46753247</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3187187.0</t>
+          <t>1460953.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2236210.2</t>
+          <t>2249872.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2043947.9</t>
+          <t>1970450.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2412556.4</t>
+          <t>2406507.48</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>192262</t>
+          <t>279422</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-120145.7216407908</t>
+          <t>-105629.0353038595</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>36859.71</v>
+        <v>-25787.26</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-33.90</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>36455264.0</t>
+          <t>37787188.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>80453830.28</t>
+          <t>78618972.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-3887846.99</v>
+        <v>-3665692.35</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,64 +6065,64 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-3.71</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-5.26</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-3.75</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>32593060.6</t>
+          <t>36455264.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>81339733.32</t>
+          <t>80453830.28</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-4991945.43</v>
+        <v>-3887846.99</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>30395369.2</t>
+          <t>32593060.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>82590132.42</t>
+          <t>81339733.32</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-6401386.67</v>
+        <v>-4991945.43</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>812.259</t>
+          <t>1046.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-20.30</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.40</t>
+          <t>-136.54</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29213195.6</t>
+          <t>30395369.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>34657603.3</t>
+          <t>33994550.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>85238942.98</t>
+          <t>82590132.42</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-5444407</t>
+          <t>-3599181</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-7526874.548620233</t>
+          <t>-7353722.566559221</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-7455976.79</v>
+        <v>-6401386.67</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>766.535</t>
+          <t>812.259</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-28.17</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-9.89</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-20.30</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-132.65</t>
+          <t>-134.40</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28359284.0</t>
+          <t>29564911.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>28928388.6</t>
+          <t>29213195.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>40272785.3</t>
+          <t>34657603.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>88728235.7</t>
+          <t>85238942.98</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-11344396</t>
+          <t>-5444407</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-7539765.049814414</t>
+          <t>-7526874.548620233</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-7906141.37</v>
+        <v>-7455976.79</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>665.622</t>
+          <t>766.535</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.58</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-26.13</t>
+          <t>-28.17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-130.65</t>
+          <t>-132.65</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>24346693.0</t>
+          <t>28359284.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31239206.4</t>
+          <t>28928388.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>42288298.0</t>
+          <t>40272785.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>92652071.9</t>
+          <t>88728235.7</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-11049091</t>
+          <t>-11344396</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-7473151.172777075</t>
+          <t>-7539765.049814414</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-8137697.12</v>
+        <v>-7906141.37</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,17 +8093,17 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>917.014</t>
+          <t>665.622</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-8.81</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-19.97</t>
+          <t>-26.13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,67 +8336,67 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>39.79</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-54.61</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-127.63</t>
+          <t>-130.65</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>32766707.0</t>
+          <t>24346693.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>35998408.4</t>
+          <t>31239206.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>44979527.8</t>
+          <t>42288298.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>112767245.36</t>
+          <t>92652071.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-8981119</t>
+          <t>-11049091</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-7352324.637023974</t>
+          <t>-7473151.172777075</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-7747938.54</v>
+        <v>-8137697.12</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>871.406</t>
+          <t>917.014</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-7.91</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-30.16</t>
+          <t>-19.97</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-70.88</t>
+          <t>-54.61</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-123.86</t>
+          <t>-127.63</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>31028383.0</t>
+          <t>32766707.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>37593731.4</t>
+          <t>35998408.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>53830704.2</t>
+          <t>44979527.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>120062941.96</t>
+          <t>112767245.36</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-16236972</t>
+          <t>-8981119</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-7280394.836870603</t>
+          <t>-7352324.637023974</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-7816572.83</v>
+        <v>-7747938.54</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>769.944</t>
+          <t>871.406</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-28.54</t>
+          <t>-30.16</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.60</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,87 +9198,87 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-5.55</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-3.49</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>36.5</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>40.04</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>37.81</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-70.88</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-4.71</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>6.33</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>37.05</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>38.88</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>37.71</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-82.93</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-119.63</t>
+          <t>-123.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>28140876.0</t>
+          <t>31028383.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>40102011.0</t>
+          <t>37593731.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>56116242.6</t>
+          <t>53830704.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>122048686.88</t>
+          <t>120062941.96</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-16014231</t>
+          <t>-16236972</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-7182907.928896697</t>
+          <t>-7280394.836870603</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-7449209.51</v>
+        <v>-7816572.83</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,17 +9386,17 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1111.919</t>
+          <t>769.944</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-28.54</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-11.60</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-100.39</t>
+          <t>-82.93</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.56</t>
+          <t>-119.63</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>39913373.0</t>
+          <t>28140876.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>51617182.0</t>
+          <t>40102011.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>60219637.4</t>
+          <t>56116242.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>123707087.1</t>
+          <t>122048686.88</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-8602455</t>
+          <t>-16014231</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-7134489.460488213</t>
+          <t>-7182907.928896697</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-6348985.81</v>
+        <v>-7449209.51</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1297.036</t>
+          <t>1111.919</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>37.41</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-108.05</t>
+          <t>-100.39</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.65</t>
+          <t>-115.56</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>246319641.4069264</t>
+          <t>246040403.2435158</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>48142703.0</t>
+          <t>39913373.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>53337389.6</t>
+          <t>51617182.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>60638983.0</t>
+          <t>60219637.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>126346717.8</t>
+          <t>123707087.1</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-7301593</t>
+          <t>-8602455</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7277308.306450214</t>
+          <t>-7134489.460488213</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-5811827.14</v>
+        <v>-6348985.81</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>16.40</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,67 +1014,67 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.74</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1862817.0</t>
+          <t>2037430.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2395938.98</t>
+          <t>2412719.42</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-22072.46</v>
+        <v>19992.97</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,64 +1455,64 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1610711.2</t>
+          <t>1862817.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2389474.58</t>
+          <t>2395938.98</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-12697.25</v>
+        <v>-22072.46</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1906,37 +1906,37 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>22.63</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
           <t>22.83</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>22.91</t>
-        </is>
-      </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1428944.2</t>
+          <t>1610711.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2349514.76</t>
+          <t>2389474.58</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-130000.86</v>
+        <v>-12697.25</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1485851.0</t>
+          <t>1428944.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2357132.54</t>
+          <t>2349514.76</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-124030.49</v>
+        <v>-130000.86</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>66.006</t>
+          <t>74.073</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1559706.4</t>
+          <t>1485851.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1953878.1</t>
+          <t>1868651.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2371167.86</t>
+          <t>2357132.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-394171</t>
+          <t>-382800</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-89111.03010474489</t>
+          <t>-94483.25454918241</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-142764.16</v>
+        <v>-124030.49</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-34.05</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.176</t>
+          <t>66.006</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-20.17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.82</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.45</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>485673.0</t>
+          <t>1514150.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1707269.8</t>
+          <t>1559706.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1978571.1</t>
+          <t>1953878.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2372228.6</t>
+          <t>2371167.86</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-271301</t>
+          <t>-394171</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-79355.91633946935</t>
+          <t>-89111.03010474489</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-145626.5</v>
+        <v>-142764.16</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-34.05</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>89.795</t>
+          <t>21.176</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-29.82</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>65.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>23.02</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
           <t>23.01</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.18</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.68</t>
+          <t>-104.45</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2061436.0</t>
+          <t>485673.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1902325.8</t>
+          <t>1707269.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2069268.0</t>
+          <t>1978571.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2377009.5</t>
+          <t>2372228.6</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-166942</t>
+          <t>-271301</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-67306.72009094176</t>
+          <t>-79355.91633946935</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-34320.64</v>
+        <v>-145626.5</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>72.437</t>
+          <t>89.795</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.59</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-104.68</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1678367.0</t>
+          <t>2061436.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2127476.0</t>
+          <t>1902325.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2027376.4</t>
+          <t>2069268.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2400065.28</t>
+          <t>2377009.5</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>100099</t>
+          <t>-166942</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-73304.18881022699</t>
+          <t>-67306.72009094176</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-42918.29</v>
+        <v>-34320.64</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-33.48</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>89.409</t>
+          <t>72.437</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.51</t>
+          <t>-28.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4462,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.19</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2058906.0</t>
+          <t>1678367.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2251451.0</t>
+          <t>2127476.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2030675.9</t>
+          <t>2027376.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2410232.12</t>
+          <t>2400065.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>220775</t>
+          <t>100099</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-78828.89719921869</t>
+          <t>-73304.18881022699</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-12624.75</v>
+        <v>-42918.29</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-34.33</t>
+          <t>-33.48</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>98.245</t>
+          <t>89.409</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-29.51</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>23.14</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.36</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>14.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-105.19</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2251967.0</t>
+          <t>2058906.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2348049.8</t>
+          <t>2251451.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2024201.0</t>
+          <t>2030675.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2424454.06</t>
+          <t>2410232.12</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>323848</t>
+          <t>220775</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-90866.01536825285</t>
+          <t>-78828.89719921869</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-9669.41</v>
+        <v>-12624.75</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-34.33</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>63.956</t>
+          <t>98.245</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.18</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>61.67</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>25.36</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.52</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19615909.46753247</t>
+          <t>19592804.16354467</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1460953.0</t>
+          <t>2251967.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2249872.4</t>
+          <t>2348049.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1970450.2</t>
+          <t>2024201.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2406507.48</t>
+          <t>2424454.06</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>279422</t>
+          <t>323848</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-105629.0353038595</t>
+          <t>-90866.01536825285</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-25787.26</v>
+        <v>-9669.41</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>79.06</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-143.27</t>
+          <t>-145.72</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>37787188.0</t>
+          <t>38043385.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>33357788.3</t>
+          <t>33628290.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>78618972.02</t>
+          <t>75765926.32</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>4429399</t>
+          <t>4415094</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-6075003.998210644</t>
+          <t>-5714467.574611069</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-3665692.35</v>
+        <v>-3731517.24</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>36455264.0</t>
+          <t>37787188.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>80453830.28</t>
+          <t>78618972.02</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-3887846.99</v>
+        <v>-3665692.35</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,64 +6496,64 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-4.21</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-7.46</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-3.71</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>32593060.6</t>
+          <t>36455264.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>81339733.32</t>
+          <t>80453830.28</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-4991945.43</v>
+        <v>-3887846.99</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>30395369.2</t>
+          <t>32593060.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>82590132.42</t>
+          <t>81339733.32</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-6401386.67</v>
+        <v>-4991945.43</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>812.259</t>
+          <t>1046.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-20.30</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-134.40</t>
+          <t>-136.54</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>29213195.6</t>
+          <t>30395369.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>34657603.3</t>
+          <t>33994550.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>85238942.98</t>
+          <t>82590132.42</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-5444407</t>
+          <t>-3599181</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-7526874.548620233</t>
+          <t>-7353722.566559221</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-7455976.79</v>
+        <v>-6401386.67</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>766.535</t>
+          <t>812.259</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-10.15</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-28.17</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-9.89</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-20.30</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-132.65</t>
+          <t>-134.40</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28359284.0</t>
+          <t>29564911.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>28928388.6</t>
+          <t>29213195.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>40272785.3</t>
+          <t>34657603.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>88728235.7</t>
+          <t>85238942.98</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-11344396</t>
+          <t>-5444407</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-7539765.049814414</t>
+          <t>-7526874.548620233</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-7906141.37</v>
+        <v>-7455976.79</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,17 +8093,17 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>665.622</t>
+          <t>766.535</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.81</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-26.13</t>
+          <t>-28.17</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-130.65</t>
+          <t>-132.65</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>24346693.0</t>
+          <t>28359284.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>31239206.4</t>
+          <t>28928388.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>42288298.0</t>
+          <t>40272785.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>92652071.9</t>
+          <t>88728235.7</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-11049091</t>
+          <t>-11344396</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-7473151.172777075</t>
+          <t>-7539765.049814414</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-8137697.12</v>
+        <v>-7906141.37</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>917.014</t>
+          <t>665.622</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.91</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-19.97</t>
+          <t>-26.13</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,67 +8767,67 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>39.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-54.61</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-127.63</t>
+          <t>-130.65</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>32766707.0</t>
+          <t>24346693.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>35998408.4</t>
+          <t>31239206.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>44979527.8</t>
+          <t>42288298.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>112767245.36</t>
+          <t>92652071.9</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-8981119</t>
+          <t>-11049091</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-7352324.637023974</t>
+          <t>-7473151.172777075</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-7747938.54</v>
+        <v>-8137697.12</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>871.406</t>
+          <t>917.014</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-30.16</t>
+          <t>-19.97</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-70.88</t>
+          <t>-54.61</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-123.86</t>
+          <t>-127.63</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>31028383.0</t>
+          <t>32766707.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>37593731.4</t>
+          <t>35998408.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>53830704.2</t>
+          <t>44979527.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>120062941.96</t>
+          <t>112767245.36</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-16236972</t>
+          <t>-8981119</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-7280394.836870603</t>
+          <t>-7352324.637023974</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-7816572.83</v>
+        <v>-7747938.54</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>769.944</t>
+          <t>871.406</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-28.54</t>
+          <t>-30.16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.60</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,87 +9629,87 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-5.55</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-3.49</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>36.5</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>40.04</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>37.81</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-70.88</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-4.71</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>6.33</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>37.05</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>38.88</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>37.71</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-82.93</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-119.63</t>
+          <t>-123.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>28140876.0</t>
+          <t>31028383.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>40102011.0</t>
+          <t>37593731.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>56116242.6</t>
+          <t>53830704.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>122048686.88</t>
+          <t>120062941.96</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-16014231</t>
+          <t>-16236972</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-7182907.928896697</t>
+          <t>-7280394.836870603</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-7449209.51</v>
+        <v>-7816572.83</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1111.919</t>
+          <t>769.944</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-28.54</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-11.60</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>893</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-100.39</t>
+          <t>-82.93</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-115.56</t>
+          <t>-119.63</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>246040403.2435158</t>
+          <t>245752962.1553957</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>39913373.0</t>
+          <t>28140876.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>51617182.0</t>
+          <t>40102011.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>60219637.4</t>
+          <t>56116242.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>123707087.1</t>
+          <t>122048686.88</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-8602455</t>
+          <t>-16014231</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7134489.460488213</t>
+          <t>-7182907.928896697</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-6348985.81</v>
+        <v>-7449209.51</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>241.631</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-25.69</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2105436.6</t>
+          <t>3014163.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1795643.8</t>
+          <t>2221553.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2426790.7</t>
+          <t>2483633.94</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-48844.01860000911</t>
+          <t>7308.07499077954</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>22121.87769018905</t>
+          <t>316144.5897401171</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2029658</v>
+        <v>5937465</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-30.77</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>106.512</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.66</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.98</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2037430.8</t>
+          <t>2105436.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1798568.6</t>
+          <t>1795643.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2412719.42</t>
+          <t>2426790.7</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-61746.90883459059</t>
+          <t>-48844.01860000911</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>19992.97198707075</t>
+          <t>22121.87769018905</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2387219</v>
+        <v>2029658</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-35.61</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,72 +1886,72 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.74</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1862817.0</t>
+          <t>2037430.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2395938.98</t>
+          <t>2412719.42</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-22072.46373120812</t>
+          <t>19992.97198707075</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1746202</v>
+        <v>2387219</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,64 +2337,64 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1610711.2</t>
+          <t>1862817.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2389474.58</t>
+          <t>2395938.98</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-12697.2481954915</t>
+          <t>-22072.46373120812</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>2970271</v>
+        <v>1746202</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,17 +2773,17 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2793,37 +2793,37 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>22.63</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>22.83</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>22.91</t>
-        </is>
-      </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1428944.2</t>
+          <t>1610711.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2349514.76</t>
+          <t>2389474.58</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-130000.8599946292</t>
+          <t>-12697.2481954915</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1393833</v>
+        <v>2970271</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,27 +3011,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1485851.0</t>
+          <t>1428944.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2357132.54</t>
+          <t>2349514.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-124030.4889935888</t>
+          <t>-130000.8599946292</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1689629</v>
+        <v>1393833</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3462,12 +3462,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>66.006</t>
+          <t>74.073</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1559706.4</t>
+          <t>1485851.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1953878.1</t>
+          <t>1868651.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2371167.86</t>
+          <t>2357132.54</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-394171</t>
+          <t>-382800</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-89111.03010474489</t>
+          <t>-94483.25454918241</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-142764.1558137604</t>
+          <t>-124030.4889935888</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1514150</v>
+        <v>1689629</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-34.05</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21.176</t>
+          <t>66.006</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-20.17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.82</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.45</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>485673.0</t>
+          <t>1514150.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1707269.8</t>
+          <t>1559706.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1978571.1</t>
+          <t>1953878.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2372228.6</t>
+          <t>2371167.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-271301</t>
+          <t>-394171</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-79355.91633946935</t>
+          <t>-89111.03010474489</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-145626.495706371</t>
+          <t>-142764.1558137604</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>485673</v>
+        <v>1514150</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-34.05</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4319,27 +4319,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>89.795</t>
+          <t>21.176</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-29.82</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>65.56</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>23.02</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
           <t>23.01</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.18</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.68</t>
+          <t>-104.45</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2061436.0</t>
+          <t>485673.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1902325.8</t>
+          <t>1707269.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2069268.0</t>
+          <t>1978571.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2377009.5</t>
+          <t>2372228.6</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-166942</t>
+          <t>-271301</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-67306.72009094176</t>
+          <t>-79355.91633946935</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-34320.64213487296</t>
+          <t>-145626.495706371</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2061436</v>
+        <v>485673</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,27 +4755,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>72.437</t>
+          <t>89.795</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-28.59</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-104.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1678367.0</t>
+          <t>2061436.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2127476.0</t>
+          <t>1902325.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2027376.4</t>
+          <t>2069268.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2400065.28</t>
+          <t>2377009.5</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>100099</t>
+          <t>-166942</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-73304.18881022699</t>
+          <t>-67306.72009094176</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-42918.29267077264</t>
+          <t>-34320.64213487296</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1678367</v>
+        <v>2061436</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-33.48</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,27 +5191,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>89.409</t>
+          <t>72.437</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.51</t>
+          <t>-28.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.19</t>
+          <t>-104.93</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19568993.6352518</t>
+          <t>19553673.52586207</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2058906.0</t>
+          <t>1678367.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2251451.0</t>
+          <t>2127476.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2030675.9</t>
+          <t>2027376.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2410232.12</t>
+          <t>2400065.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>220775</t>
+          <t>100099</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-78828.89719921869</t>
+          <t>-73304.18881022699</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-12624.74726953078</t>
+          <t>-42918.29267077264</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2058906</v>
+        <v>1678367</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-34.33</t>
+          <t>-33.48</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>76.97</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1012.715</t>
+          <t>604.193</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-148.57</t>
+          <t>-151.13</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>37394546.6</t>
+          <t>32668185.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>33894957.9</t>
+          <t>32630623.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>74635589.06</t>
+          <t>73222858.24</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3499588</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-5369260.226993212</t>
+          <t>-5192313.033442677</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3470619.815095</t>
+          <t>-4219103.468914736</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>33695057</v>
+        <v>20123359</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>893.111</t>
+          <t>1012.715</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,37 +6266,37 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6306,17 +6306,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-145.72</t>
+          <t>-148.57</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>38043385.4</t>
+          <t>37394546.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>33628290.5</t>
+          <t>33894957.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>75765926.32</t>
+          <t>74635589.06</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4415094</t>
+          <t>3499588</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-5714467.574611069</t>
+          <t>-5369260.226993212</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3731517.244813405</t>
+          <t>-3470619.815095</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>30845898</v>
+        <v>33695057</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.96</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-143.27</t>
+          <t>-145.72</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>37787188.0</t>
+          <t>38043385.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33357788.3</t>
+          <t>33628290.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>78618972.02</t>
+          <t>75765926.32</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4429399</t>
+          <t>4415094</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-6075003.998210644</t>
+          <t>-5714467.574611069</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3665692.349953502</t>
+          <t>-3731517.244813405</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>35018904</v>
+        <v>30845898</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>36455264.0</t>
+          <t>37787188.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>80453830.28</t>
+          <t>78618972.02</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3887846.987655312</t>
+          <t>-3665692.349953502</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>43657710</v>
+        <v>35018904</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,64 +7438,64 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-5.08</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-8.6</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-5.18</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>32593060.6</t>
+          <t>36455264.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>81339733.32</t>
+          <t>80453830.28</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-4991945.43481306</t>
+          <t>-3887846.987655312</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>43755164</v>
+        <v>43657710</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>30395369.2</t>
+          <t>32593060.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>82590132.42</t>
+          <t>81339733.32</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-6401386.665223651</t>
+          <t>-4991945.43481306</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>36939251</v>
+        <v>43755164</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>812.259</t>
+          <t>1046.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-20.30</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-134.40</t>
+          <t>-136.54</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>29213195.6</t>
+          <t>30395369.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>34657603.3</t>
+          <t>33994550.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>85238942.98</t>
+          <t>82590132.42</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-5444407</t>
+          <t>-3599181</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-7526874.548620233</t>
+          <t>-7353722.566559221</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-7455976.792052239</t>
+          <t>-6401386.665223651</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>29564911</v>
+        <v>36939251</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>766.535</t>
+          <t>812.259</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-7.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-28.17</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-9.89</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-20.30</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-132.65</t>
+          <t>-134.40</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>28359284.0</t>
+          <t>29564911.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>28928388.6</t>
+          <t>29213195.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>40272785.3</t>
+          <t>34657603.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>88728235.7</t>
+          <t>85238942.98</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-11344396</t>
+          <t>-5444407</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-7539765.049814414</t>
+          <t>-7526874.548620233</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-7906141.373519778</t>
+          <t>-7455976.792052239</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>28359284</v>
+        <v>29564911</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>665.622</t>
+          <t>766.535</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-9.99</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-26.13</t>
+          <t>-28.17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-130.65</t>
+          <t>-132.65</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>24346693.0</t>
+          <t>28359284.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>31239206.4</t>
+          <t>28928388.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>42288298.0</t>
+          <t>40272785.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>92652071.9</t>
+          <t>88728235.7</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-11049091</t>
+          <t>-11344396</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-7473151.172777075</t>
+          <t>-7539765.049814414</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-8137697.119419128</t>
+          <t>-7906141.373519778</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>24346693</v>
+        <v>28359284</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>917.014</t>
+          <t>665.622</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-19.97</t>
+          <t>-26.13</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,67 +9734,67 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>39.79</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-54.61</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-127.63</t>
+          <t>-130.65</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>32766707.0</t>
+          <t>24346693.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>35998408.4</t>
+          <t>31239206.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>44979527.8</t>
+          <t>42288298.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>112767245.36</t>
+          <t>92652071.9</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-8981119</t>
+          <t>-11049091</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-7352324.637023974</t>
+          <t>-7473151.172777075</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-7747938.537867516</t>
+          <t>-8137697.119419128</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>32766707</v>
+        <v>24346693</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>871.406</t>
+          <t>917.014</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-30.16</t>
+          <t>-19.97</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>604</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-70.88</t>
+          <t>-54.61</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-123.86</t>
+          <t>-127.63</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>245472487.4762931</t>
+          <t>245163610.2180775</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>31028383.0</t>
+          <t>32766707.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>37593731.4</t>
+          <t>35998408.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>53830704.2</t>
+          <t>44979527.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>120062941.96</t>
+          <t>112767245.36</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-16236972</t>
+          <t>-8981119</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7280394.836870603</t>
+          <t>-7352324.637023974</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-7816572.830727085</t>
+          <t>-7747938.537867516</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>31028383</v>
+        <v>32766707</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>241.631</t>
+          <t>226.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-24.31</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>96.15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3014163.0</t>
+          <t>3544313.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2221553.6</t>
+          <t>2577512.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2483633.94</t>
+          <t>2550509.38</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>966800</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7308.07499077954</t>
+          <t>81618.15167397709</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>316144.5897401171</t>
+          <t>490323.5734315636</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>5937465</v>
+        <v>5621021</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>241.631</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-25.69</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2105436.6</t>
+          <t>3014163.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1795643.8</t>
+          <t>2221553.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2426790.7</t>
+          <t>2483633.94</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-48844.01860000911</t>
+          <t>7308.07499077954</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>22121.87769018905</t>
+          <t>316144.5897401171</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2029658</v>
+        <v>5937465</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-30.77</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>106.512</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.66</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.98</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2037430.8</t>
+          <t>2105436.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1798568.6</t>
+          <t>1795643.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2412719.42</t>
+          <t>2426790.7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-61746.90883459059</t>
+          <t>-48844.01860000911</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>19992.97198707075</t>
+          <t>22121.87769018905</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>2387219</v>
+        <v>2029658</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-35.61</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,67 +2327,67 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.74</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1862817.0</t>
+          <t>2037430.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2395938.98</t>
+          <t>2412719.42</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-22072.46373120812</t>
+          <t>19992.97198707075</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1746202</v>
+        <v>2387219</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,64 +2773,64 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1610711.2</t>
+          <t>1862817.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2389474.58</t>
+          <t>2395938.98</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-12697.2481954915</t>
+          <t>-22072.46373120812</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>2970271</v>
+        <v>1746202</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,17 +3209,17 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>22.63</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>22.83</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>22.91</t>
-        </is>
-      </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1428944.2</t>
+          <t>1610711.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2349514.76</t>
+          <t>2389474.58</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-130000.8599946292</t>
+          <t>-12697.2481954915</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1393833</v>
+        <v>2970271</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1485851.0</t>
+          <t>1428944.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2357132.54</t>
+          <t>2349514.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-124030.4889935888</t>
+          <t>-130000.8599946292</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1689629</v>
+        <v>1393833</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>66.006</t>
+          <t>74.073</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1559706.4</t>
+          <t>1485851.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1953878.1</t>
+          <t>1868651.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2371167.86</t>
+          <t>2357132.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-394171</t>
+          <t>-382800</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-89111.03010474489</t>
+          <t>-94483.25454918241</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-142764.1558137604</t>
+          <t>-124030.4889935888</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1514150</v>
+        <v>1689629</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-34.05</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21.176</t>
+          <t>66.006</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-20.17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.82</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.45</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>485673.0</t>
+          <t>1514150.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1707269.8</t>
+          <t>1559706.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1978571.1</t>
+          <t>1953878.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2372228.6</t>
+          <t>2371167.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-271301</t>
+          <t>-394171</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-79355.91633946935</t>
+          <t>-89111.03010474489</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-145626.495706371</t>
+          <t>-142764.1558137604</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>485673</v>
+        <v>1514150</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-34.05</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>89.795</t>
+          <t>21.176</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-29.82</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>65.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>23.02</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
           <t>23.01</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.18</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.68</t>
+          <t>-104.45</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2061436.0</t>
+          <t>485673.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1902325.8</t>
+          <t>1707269.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2069268.0</t>
+          <t>1978571.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2377009.5</t>
+          <t>2372228.6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-166942</t>
+          <t>-271301</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-67306.72009094176</t>
+          <t>-79355.91633946935</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-34320.64213487296</t>
+          <t>-145626.495706371</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2061436</v>
+        <v>485673</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>72.437</t>
+          <t>89.795</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.59</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.93</t>
+          <t>-104.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19553673.52586207</t>
+          <t>19537716.36370158</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1678367.0</t>
+          <t>2061436.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2127476.0</t>
+          <t>1902325.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2027376.4</t>
+          <t>2069268.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2400065.28</t>
+          <t>2377009.5</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>100099</t>
+          <t>-166942</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-73304.18881022699</t>
+          <t>-67306.72009094176</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-42918.29267077264</t>
+          <t>-34320.64213487296</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1678367</v>
+        <v>2061436</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-33.48</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>76.97</t>
+          <t>78.34</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>604.193</t>
+          <t>494.417</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,72 +5815,72 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>33.76000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.51</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-13.17</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-151.13</t>
+          <t>-152.87</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>32668185.6</t>
+          <t>27292993.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>32630623.1</t>
+          <t>31874128.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>73222858.24</t>
+          <t>72125013.6</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>-4581135</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-5192313.033442677</t>
+          <t>-5145524.157507756</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-4219103.468914736</t>
+          <t>-4888185.339865692</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>20123359</v>
+        <v>16781747</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1012.715</t>
+          <t>604.193</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,72 +6251,72 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-148.57</t>
+          <t>-151.13</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>37394546.6</t>
+          <t>32668185.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>33894957.9</t>
+          <t>32630623.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>74635589.06</t>
+          <t>73222858.24</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>3499588</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-5369260.226993212</t>
+          <t>-5192313.033442677</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3470619.815095</t>
+          <t>-4219103.468914736</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>33695057</v>
+        <v>20123359</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>893.111</t>
+          <t>1012.715</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,37 +6702,37 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-145.72</t>
+          <t>-148.57</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>38043385.4</t>
+          <t>37394546.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33628290.5</t>
+          <t>33894957.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>75765926.32</t>
+          <t>74635589.06</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4415094</t>
+          <t>3499588</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5714467.574611069</t>
+          <t>-5369260.226993212</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3731517.244813405</t>
+          <t>-3470619.815095</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>30845898</v>
+        <v>33695057</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,72 +7123,72 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.96</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-143.27</t>
+          <t>-145.72</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>37787188.0</t>
+          <t>38043385.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>33357788.3</t>
+          <t>33628290.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>78618972.02</t>
+          <t>75765926.32</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4429399</t>
+          <t>4415094</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6075003.998210644</t>
+          <t>-5714467.574611069</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3665692.349953502</t>
+          <t>-3731517.244813405</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>35018904</v>
+        <v>30845898</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>36455264.0</t>
+          <t>37787188.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>80453830.28</t>
+          <t>78618972.02</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3887846.987655312</t>
+          <t>-3665692.349953502</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>43657710</v>
+        <v>35018904</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,64 +7874,64 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-5.22</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-7.3</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-5.08</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,72 +7995,72 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>32593060.6</t>
+          <t>36455264.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>81339733.32</t>
+          <t>80453830.28</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-4991945.43481306</t>
+          <t>-3887846.987655312</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>43755164</v>
+        <v>43657710</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,72 +8431,72 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30395369.2</t>
+          <t>32593060.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>82590132.42</t>
+          <t>81339733.32</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-6401386.665223651</t>
+          <t>-4991945.43481306</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>36939251</v>
+        <v>43755164</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>812.259</t>
+          <t>1046.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.6</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,72 +8867,72 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-20.30</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-134.40</t>
+          <t>-136.54</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>29213195.6</t>
+          <t>30395369.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>34657603.3</t>
+          <t>33994550.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>85238942.98</t>
+          <t>82590132.42</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-5444407</t>
+          <t>-3599181</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-7526874.548620233</t>
+          <t>-7353722.566559221</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-7455976.792052239</t>
+          <t>-6401386.665223651</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>29564911</v>
+        <v>36939251</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>766.535</t>
+          <t>812.259</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.99</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-28.17</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-9.89</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,72 +9303,72 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-20.30</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-132.65</t>
+          <t>-134.40</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>28359284.0</t>
+          <t>29564911.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>28928388.6</t>
+          <t>29213195.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>40272785.3</t>
+          <t>34657603.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>88728235.7</t>
+          <t>85238942.98</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-11344396</t>
+          <t>-5444407</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-7539765.049814414</t>
+          <t>-7526874.548620233</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-7906141.373519778</t>
+          <t>-7455976.792052239</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>28359284</v>
+        <v>29564911</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>665.622</t>
+          <t>766.535</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-26.13</t>
+          <t>-28.17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,72 +9739,72 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-130.65</t>
+          <t>-132.65</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>24346693.0</t>
+          <t>28359284.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>31239206.4</t>
+          <t>28928388.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>42288298.0</t>
+          <t>40272785.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>92652071.9</t>
+          <t>88728235.7</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-11049091</t>
+          <t>-11344396</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-7473151.172777075</t>
+          <t>-7539765.049814414</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-8137697.119419128</t>
+          <t>-7906141.373519778</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>24346693</v>
+        <v>28359284</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>917.014</t>
+          <t>665.622</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-19.97</t>
+          <t>-26.13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,62 +10175,62 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>39.79</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-54.61</t>
+          <t>-39.39</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-127.63</t>
+          <t>-130.65</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>245163610.2180775</t>
+          <t>244848436.8803725</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>32766707.0</t>
+          <t>24346693.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>35998408.4</t>
+          <t>31239206.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>44979527.8</t>
+          <t>42288298.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>112767245.36</t>
+          <t>92652071.9</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-8981119</t>
+          <t>-11049091</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7352324.637023974</t>
+          <t>-7473151.172777075</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-7747938.537867516</t>
+          <t>-8137697.119419128</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>32766707</v>
+        <v>24346693</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>226.67</t>
+          <t>183.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.31</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>96.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>24.01</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>167.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-102.01</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3544313.0</t>
+          <t>4123414.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2577512.1</t>
+          <t>2993115.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2550509.38</t>
+          <t>2501026.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>966800</t>
+          <t>1130298</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>81618.15167397709</t>
+          <t>150068.0433671787</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>490323.5734315636</t>
+          <t>526542.4476797874</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>5621021</v>
+        <v>4641710</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-27.64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>241.631</t>
+          <t>226.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-24.31</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>96.15</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3014163.0</t>
+          <t>3544313.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2221553.6</t>
+          <t>2577512.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2483633.94</t>
+          <t>2550509.38</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>966800</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7308.07499077954</t>
+          <t>81618.15167397709</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>316144.5897401171</t>
+          <t>490323.5734315636</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5937465</v>
+        <v>5621021</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>241.631</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-25.69</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2105436.6</t>
+          <t>3014163.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1795643.8</t>
+          <t>2221553.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2426790.7</t>
+          <t>2483633.94</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-48844.01860000911</t>
+          <t>7308.07499077954</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>22121.87769018905</t>
+          <t>316144.5897401171</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>2029658</v>
+        <v>5937465</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-30.77</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>106.512</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.66</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.98</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2037430.8</t>
+          <t>2105436.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1798568.6</t>
+          <t>1795643.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2412719.42</t>
+          <t>2426790.7</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-61746.90883459059</t>
+          <t>-48844.01860000911</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>19992.97198707075</t>
+          <t>22121.87769018905</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>2387219</v>
+        <v>2029658</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-35.61</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,72 +2758,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.74</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1862817.0</t>
+          <t>2037430.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2395938.98</t>
+          <t>2412719.42</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-22072.46373120812</t>
+          <t>19992.97198707075</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1746202</v>
+        <v>2387219</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,64 +3209,64 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1610711.2</t>
+          <t>1862817.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2389474.58</t>
+          <t>2395938.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-12697.2481954915</t>
+          <t>-22072.46373120812</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>2970271</v>
+        <v>1746202</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3665,37 +3665,37 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>22.63</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
           <t>22.83</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>22.91</t>
-        </is>
-      </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1428944.2</t>
+          <t>1610711.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2349514.76</t>
+          <t>2389474.58</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-130000.8599946292</t>
+          <t>-12697.2481954915</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1393833</v>
+        <v>2970271</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1485851.0</t>
+          <t>1428944.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2357132.54</t>
+          <t>2349514.76</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-124030.4889935888</t>
+          <t>-130000.8599946292</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1689629</v>
+        <v>1393833</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>66.006</t>
+          <t>74.073</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1559706.4</t>
+          <t>1485851.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1953878.1</t>
+          <t>1868651.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2371167.86</t>
+          <t>2357132.54</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-394171</t>
+          <t>-382800</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-89111.03010474489</t>
+          <t>-94483.25454918241</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-142764.1558137604</t>
+          <t>-124030.4889935888</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1514150</v>
+        <v>1689629</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-34.05</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21.176</t>
+          <t>66.006</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-20.17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.82</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.45</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>485673.0</t>
+          <t>1514150.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1707269.8</t>
+          <t>1559706.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1978571.1</t>
+          <t>1953878.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2372228.6</t>
+          <t>2371167.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-271301</t>
+          <t>-394171</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-79355.91633946935</t>
+          <t>-89111.03010474489</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-145626.495706371</t>
+          <t>-142764.1558137604</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>485673</v>
+        <v>1514150</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-34.05</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>89.795</t>
+          <t>21.176</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-29.82</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>65.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>23.02</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
           <t>23.01</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.18</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.68</t>
+          <t>-104.45</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19537716.36370158</t>
+          <t>19519700.38753582</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2061436.0</t>
+          <t>485673.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1902325.8</t>
+          <t>1707269.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2069268.0</t>
+          <t>1978571.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2377009.5</t>
+          <t>2372228.6</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-166942</t>
+          <t>-271301</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-67306.72009094176</t>
+          <t>-79355.91633946935</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-34320.64213487296</t>
+          <t>-145626.495706371</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2061436</v>
+        <v>485673</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-34.62</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>78.34</t>
+          <t>79.73</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>494.417</t>
+          <t>579.265</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-21.69</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>33.76000000000001</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>38.51</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-13.17</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-152.87</t>
+          <t>-153.33</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27292993.0</t>
+          <t>24319072.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31874128.5</t>
+          <t>31053130.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>72125013.6</t>
+          <t>70329347.68</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4581135</t>
+          <t>-6734057</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-5145524.157507756</t>
+          <t>-5120331.424204211</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-4888185.339865692</t>
+          <t>-4981771.391034715</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>16781747</v>
+        <v>20149302</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>604.193</t>
+          <t>494.417</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>33.76000000000001</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.51</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-13.17</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-151.13</t>
+          <t>-152.87</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>32668185.6</t>
+          <t>27292993.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>32630623.1</t>
+          <t>31874128.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>73222858.24</t>
+          <t>72125013.6</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>-4581135</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-5192313.033442677</t>
+          <t>-5145524.157507756</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-4219103.468914736</t>
+          <t>-4888185.339865692</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>20123359</v>
+        <v>16781747</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1012.715</t>
+          <t>604.193</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-148.57</t>
+          <t>-151.13</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>37394546.6</t>
+          <t>32668185.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33894957.9</t>
+          <t>32630623.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>74635589.06</t>
+          <t>73222858.24</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3499588</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5369260.226993212</t>
+          <t>-5192313.033442677</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3470619.815095</t>
+          <t>-4219103.468914736</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>33695057</v>
+        <v>20123359</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>893.111</t>
+          <t>1012.715</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,17 +7118,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,37 +7138,37 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7178,17 +7178,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-145.72</t>
+          <t>-148.57</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>38043385.4</t>
+          <t>37394546.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>33628290.5</t>
+          <t>33894957.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>75765926.32</t>
+          <t>74635589.06</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4415094</t>
+          <t>3499588</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5714467.574611069</t>
+          <t>-5369260.226993212</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3731517.244813405</t>
+          <t>-3470619.815095</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>30845898</v>
+        <v>33695057</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.96</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-143.27</t>
+          <t>-145.72</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>37787188.0</t>
+          <t>38043385.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>33357788.3</t>
+          <t>33628290.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>78618972.02</t>
+          <t>75765926.32</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4429399</t>
+          <t>4415094</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6075003.998210644</t>
+          <t>-5714467.574611069</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3665692.349953502</t>
+          <t>-3731517.244813405</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>35018904</v>
+        <v>30845898</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>36455264.0</t>
+          <t>37787188.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>80453830.28</t>
+          <t>78618972.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3887846.987655312</t>
+          <t>-3665692.349953502</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>43657710</v>
+        <v>35018904</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,64 +8310,64 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-4.33</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-5.57</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-5.22</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>32593060.6</t>
+          <t>36455264.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>81339733.32</t>
+          <t>80453830.28</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-4991945.43481306</t>
+          <t>-3887846.987655312</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>43755164</v>
+        <v>43657710</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>30395369.2</t>
+          <t>32593060.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>82590132.42</t>
+          <t>81339733.32</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-6401386.665223651</t>
+          <t>-4991945.43481306</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>36939251</v>
+        <v>43755164</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>812.259</t>
+          <t>1046.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-20.30</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-134.40</t>
+          <t>-136.54</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>29213195.6</t>
+          <t>30395369.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>34657603.3</t>
+          <t>33994550.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>85238942.98</t>
+          <t>82590132.42</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-5444407</t>
+          <t>-3599181</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-7526874.548620233</t>
+          <t>-7353722.566559221</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-7455976.792052239</t>
+          <t>-6401386.665223651</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>29564911</v>
+        <v>36939251</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>766.535</t>
+          <t>812.259</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-28.17</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-9.89</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-20.30</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-132.65</t>
+          <t>-134.40</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>28359284.0</t>
+          <t>29564911.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>28928388.6</t>
+          <t>29213195.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>40272785.3</t>
+          <t>34657603.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>88728235.7</t>
+          <t>85238942.98</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-11344396</t>
+          <t>-5444407</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-7539765.049814414</t>
+          <t>-7526874.548620233</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-7906141.373519778</t>
+          <t>-7455976.792052239</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>28359284</v>
+        <v>29564911</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>665.622</t>
+          <t>766.535</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-26.13</t>
+          <t>-28.17</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>579</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.29000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-39.39</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-130.65</t>
+          <t>-132.65</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>244848436.8803725</t>
+          <t>244541391.8390558</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>24346693.0</t>
+          <t>28359284.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>31239206.4</t>
+          <t>28928388.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>42288298.0</t>
+          <t>40272785.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>92652071.9</t>
+          <t>88728235.7</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-11049091</t>
+          <t>-11344396</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7473151.172777075</t>
+          <t>-7539765.049814414</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-8137697.119419128</t>
+          <t>-7906141.373519778</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>24346693</v>
+        <v>28359284</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>24.01</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>23.07</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>23.63</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>23.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>4641710.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4123414.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4123414.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2993115.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2501026.3</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2501026.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>526542.4476797874</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>4641710</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>4641710.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>23.3</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>23.62</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>23.62</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5621021.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>3544313.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>3544313</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2577512.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2550509.38</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2550509.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>490323.5734315636</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5621021</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5621021.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>23.65</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>23.65</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>5937465.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3014163.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3014163</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>2221553.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2483633.94</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2483633.94</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>316144.5897401171</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>5937465</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>5937465.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>22.32</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>22.77</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>23.68</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>23.68</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>2029658.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2105436.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2105436.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1795643.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2426790.7</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2426790.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>22121.87769018905</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>2029658</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2029658.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>22.3</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>22.76</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>23.74</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>23.74</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2387219.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2037430.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2037430.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1798568.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2412719.42</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2412719.42</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>19992.97198707075</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2387219</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2387219.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>22.41</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>22.77</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>23.81</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>1746202.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1862817.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1862817</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1785043.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2395938.98</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2395938.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-22072.46373120812</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>1746202</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1746202.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>22.63</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>22.83</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>23.9</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>23.9</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2970271.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1610711.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1610711.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1756518.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2389474.58</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2389474.58</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-12697.2481954915</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2970271</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2970271.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>22.83</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>22.91</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>23.98</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>23.98</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1393833.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1428944.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1428944.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1778210.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2349514.76</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2349514.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-130000.8599946292</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1393833</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1393833.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>23.05</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>22.96</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>24.05</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1689629.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1485851.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1485851</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1868651.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2357132.54</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2357132.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-124030.4889935888</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1689629</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1689629.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>23.08</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>22.99</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>24.11</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>24.11</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1514150.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1559706.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1559706.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1953878.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2371167.86</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2371167.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-142764.1558137604</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1514150</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1514150.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>23.02</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>23.01</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>24.18</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>24.18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>485673.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1707269.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1707269.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1978571.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2372228.6</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2372228.6</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-145626.495706371</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>485673</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>485673.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>34.04</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>35.68</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>38.41</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>20149302.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>24319072.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>24319072.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>31053130.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>70329347.68</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>70329347.68000001</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-4981771.391034715</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>20149302</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>20149302.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>33.76000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>38.51</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>38.51</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>16781747.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>27292993.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>27292993</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>31874128.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>72125013.6</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>72125013.59999999</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-4888185.339865692</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>16781747</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>16781747.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>33.78</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>38.66</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>38.66</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>20123359.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>32668185.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>32668185.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>32630623.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>73222858.24</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>73222858.23999999</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-4219103.468914736</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>20123359</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>20123359.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>34.27</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>36.49</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>36.49</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>38.8</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>33695057.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>37394546.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>37394546.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>33894957.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>74635589.06</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>74635589.06</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-3470619.815095</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>33695057</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>33695057.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>34.65</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>38.96</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>38.96</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>30845898.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>38043385.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>38043385.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>33628290.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>75765926.32</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>75765926.31999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-3731517.244813405</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>30845898</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>30845898.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>34.97</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>37.03</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>39.1</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>35018904.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>37787188.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>37787188</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>33357788.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>78618972.02</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>78618972.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-3665692.349953502</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>35018904</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>35018904.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>35.65</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>37.34</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>39.24</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>39.24</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>43657710.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>36455264.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>36455264</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>33847235.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>80453830.28</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>80453830.28</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-3887846.987655312</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>43657710</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>43657710.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>36.1</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>37.58</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>39.37</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>39.37</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>43755164.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>32593060.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>32593060.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>34295734.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>81339733.32</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>81339733.31999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-4991945.43481306</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>43755164</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>43755164.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>36.13</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>37.74</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>39.46</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>37.74</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>39.46</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>36939251.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>30395369.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>30395369.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>33994550.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>82590132.42</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>82590132.42</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-6401386.665223651</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>36939251</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>36939251.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>36.27</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>39.57</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>29564911.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>29213195.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>29213195.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>34657603.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>85238942.98</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>85238942.98</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-7455976.792052239</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>29564911</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>29564911.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>36.29000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>38.14</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>39.7</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>28359284.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>28928388.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>28928388.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>40272785.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>88728235.7</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>88728235.7</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-7906141.373519778</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>28359284</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>28359284.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>183.67</t>
+          <t>178.701</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.07</v>
+        <v>23.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.63</v>
+        <v>23.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>167.29</t>
+          <t>356.05</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.01</t>
+          <t>-101.07</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4123414.6</v>
+        <v>4533817.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2993115.8</t>
+          <t>3285624.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2501026.3</v>
+        <v>2558192.82</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1130298</t>
+          <t>1248193</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>150068.0433671787</t>
+          <t>207526.2403047743</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>526542.4476797874</t>
+          <t>523546.3234615498</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-27.64</t>
+          <t>-27.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>226.67</t>
+          <t>183.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.31</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>96.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>24.01</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.95</v>
+        <v>23.07</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.62</v>
+        <v>23.63</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>167.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-102.01</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3544313</v>
+        <v>4123414.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2577512.1</t>
+          <t>2993115.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2550509.38</v>
+        <v>2501026.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>966800</t>
+          <t>1130298</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>81618.15167397709</t>
+          <t>150068.0433671787</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>490323.5734315636</t>
+          <t>526542.4476797874</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-27.64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>241.631</t>
+          <t>226.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-24.31</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>96.15</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.86</v>
+        <v>22.95</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.65</v>
+        <v>23.62</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3014163</v>
+        <v>3544313</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2221553.6</t>
+          <t>2577512.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2483633.94</v>
+        <v>2550509.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>966800</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7308.07499077954</t>
+          <t>81618.15167397709</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>316144.5897401171</t>
+          <t>490323.5734315636</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>241.631</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-25.69</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.77</v>
+        <v>22.86</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.68</v>
+        <v>23.65</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2105436.6</v>
+        <v>3014163</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1795643.8</t>
+          <t>2221553.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2426790.7</v>
+        <v>2483633.94</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-48844.01860000911</t>
+          <t>7308.07499077954</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>22121.87769018905</t>
+          <t>316144.5897401171</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-30.77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>106.512</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.66</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.76</v>
+        <v>22.77</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.74</v>
+        <v>23.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.98</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2037430.8</v>
+        <v>2105436.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1798568.6</t>
+          <t>1795643.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2412719.42</v>
+        <v>2426790.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-61746.90883459059</t>
+          <t>-48844.01860000911</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>19992.97198707075</t>
+          <t>22121.87769018905</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-35.61</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,68 +3164,68 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.77</v>
+        <v>22.76</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.81</v>
+        <v>23.74</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1862817</v>
+        <v>2037430.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2395938.98</v>
+        <v>2412719.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-22072.46373120812</t>
+          <t>19992.97198707075</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,60 +3609,60 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.83</v>
+        <v>22.77</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.9</v>
+        <v>23.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1610711.2</v>
+        <v>1862817</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2389474.58</v>
+        <v>2395938.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-12697.2481954915</t>
+          <t>-22072.46373120812</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,17 +4039,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4059,33 +4059,33 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.91</v>
+        <v>22.83</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.98</v>
+        <v>23.9</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1428944.2</v>
+        <v>1610711.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2349514.76</v>
+        <v>2389474.58</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-130000.8599946292</t>
+          <t>-12697.2481954915</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.96</v>
+        <v>22.91</v>
       </c>
       <c r="AN10" t="n">
-        <v>24.05</v>
+        <v>23.98</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1485851</v>
+        <v>1428944.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2357132.54</v>
+        <v>2349514.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-124030.4889935888</t>
+          <t>-130000.8599946292</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>66.006</t>
+          <t>74.073</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.99</v>
+        <v>22.96</v>
       </c>
       <c r="AN11" t="n">
-        <v>24.11</v>
+        <v>24.05</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1559706.4</v>
+        <v>1485851</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1953878.1</t>
+          <t>1868651.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2371167.86</v>
+        <v>2357132.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-394171</t>
+          <t>-382800</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-89111.03010474489</t>
+          <t>-94483.25454918241</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-142764.1558137604</t>
+          <t>-124030.4889935888</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-34.05</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21.176</t>
+          <t>66.006</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-20.17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.82</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>23.01</v>
+        <v>22.99</v>
       </c>
       <c r="AN12" t="n">
-        <v>24.18</v>
+        <v>24.11</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.45</t>
+          <t>-104.19</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19519700.38753582</t>
+          <t>19501301.45922747</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>485673.0</t>
+          <t>1514150.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1707269.8</v>
+        <v>1559706.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1978571.1</t>
+          <t>1953878.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2372228.6</v>
+        <v>2371167.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-271301</t>
+          <t>-394171</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-79355.91633946935</t>
+          <t>-89111.03010474489</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-145626.495706371</t>
+          <t>-142764.1558137604</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>485673.0</t>
+          <t>1514150.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-34.05</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>579.265</t>
+          <t>480.416</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-21.69</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-13.43</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>35.68</v>
+        <v>35.55</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.41</v>
+        <v>38.31</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-153.33</t>
+          <t>-152.46</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>24319072.6</v>
+        <v>21539363.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31053130.3</t>
+          <t>29791374.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>70329347.68000001</v>
+        <v>69388853.84</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-6734057</t>
+          <t>-8252010</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-5120331.424204211</t>
+          <t>-5126877.888492357</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-4981771.391034715</t>
+          <t>-5162883.44207716</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>494.417</t>
+          <t>579.265</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-21.69</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>33.76000000000001</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.51</v>
+        <v>38.41</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-13.17</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-152.87</t>
+          <t>-153.33</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>27292993</v>
+        <v>24319072.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>31874128.5</t>
+          <t>31053130.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>72125013.59999999</v>
+        <v>70329347.68000001</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-4581135</t>
+          <t>-6734057</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-5145524.157507756</t>
+          <t>-5120331.424204211</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-4888185.339865692</t>
+          <t>-4981771.391034715</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>604.193</t>
+          <t>494.417</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>33.76000000000001</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>36.15</v>
+        <v>35.88</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.66</v>
+        <v>38.51</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-13.17</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-151.13</t>
+          <t>-152.87</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>32668185.6</v>
+        <v>27292993</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>32630623.1</t>
+          <t>31874128.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>73222858.23999999</v>
+        <v>72125013.59999999</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>-4581135</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5192313.033442677</t>
+          <t>-5145524.157507756</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-4219103.468914736</t>
+          <t>-4888185.339865692</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1012.715</t>
+          <t>604.193</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>36.49</v>
+        <v>36.15</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.8</v>
+        <v>38.66</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-148.57</t>
+          <t>-151.13</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>37394546.6</v>
+        <v>32668185.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>33894957.9</t>
+          <t>32630623.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>74635589.06</v>
+        <v>73222858.23999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3499588</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5369260.226993212</t>
+          <t>-5192313.033442677</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3470619.815095</t>
+          <t>-4219103.468914736</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>893.111</t>
+          <t>1012.715</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,34 +7484,34 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>36.78</v>
+        <v>36.49</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.96</v>
+        <v>38.8</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-145.72</t>
+          <t>-148.57</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>38043385.4</v>
+        <v>37394546.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>33628290.5</t>
+          <t>33894957.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>75765926.31999999</v>
+        <v>74635589.06</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4415094</t>
+          <t>3499588</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5714467.574611069</t>
+          <t>-5369260.226993212</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3731517.244813405</t>
+          <t>-3470619.815095</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>37.03</v>
+        <v>36.78</v>
       </c>
       <c r="AN18" t="n">
-        <v>39.1</v>
+        <v>38.96</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-143.27</t>
+          <t>-145.72</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>37787188</v>
+        <v>38043385.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33357788.3</t>
+          <t>33628290.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>78618972.02</v>
+        <v>75765926.31999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4429399</t>
+          <t>4415094</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6075003.998210644</t>
+          <t>-5714467.574611069</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3665692.349953502</t>
+          <t>-3731517.244813405</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>37.34</v>
+        <v>37.03</v>
       </c>
       <c r="AN19" t="n">
-        <v>39.24</v>
+        <v>39.1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>36455264</v>
+        <v>37787188</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>80453830.28</v>
+        <v>78618972.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3887846.987655312</t>
+          <t>-3665692.349953502</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,64 +8638,64 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-4.59</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-3.15</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-4.33</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>37.58</v>
+        <v>37.34</v>
       </c>
       <c r="AN20" t="n">
-        <v>39.37</v>
+        <v>39.24</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>32593060.6</v>
+        <v>36455264</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>81339733.31999999</v>
+        <v>80453830.28</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-4991945.43481306</t>
+          <t>-3887846.987655312</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>37.74</v>
+        <v>37.58</v>
       </c>
       <c r="AN21" t="n">
-        <v>39.46</v>
+        <v>39.37</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>30395369.2</v>
+        <v>32593060.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>82590132.42</v>
+        <v>81339733.31999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-6401386.665223651</t>
+          <t>-4991945.43481306</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>812.259</t>
+          <t>1046.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>38</v>
+        <v>37.74</v>
       </c>
       <c r="AN22" t="n">
-        <v>39.57</v>
+        <v>39.46</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-20.30</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-134.40</t>
+          <t>-136.54</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>29213195.6</v>
+        <v>30395369.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>34657603.3</t>
+          <t>33994550.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>85238942.98</v>
+        <v>82590132.42</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-5444407</t>
+          <t>-3599181</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-7526874.548620233</t>
+          <t>-7353722.566559221</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-7455976.792052239</t>
+          <t>-6401386.665223651</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>766.535</t>
+          <t>812.259</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-28.17</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-9.89</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>36.29000000000001</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>38.14</v>
+        <v>38</v>
       </c>
       <c r="AN23" t="n">
-        <v>39.7</v>
+        <v>39.57</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-20.30</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-132.65</t>
+          <t>-134.40</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>244541391.8390558</t>
+          <t>244228362.7521428</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>28359284.0</t>
+          <t>29564911.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>28928388.6</v>
+        <v>29213195.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>40272785.3</t>
+          <t>34657603.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>88728235.7</v>
+        <v>85238942.98</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-11344396</t>
+          <t>-5444407</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7539765.049814414</t>
+          <t>-7526874.548620233</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-7906141.373519778</t>
+          <t>-7455976.792052239</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>28359284.0</t>
+          <t>29564911.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>178.701</t>
+          <t>91.896</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-23.70</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.22</v>
+        <v>23.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.64</v>
+        <v>23.66</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>356.05</t>
+          <t>2035.51</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.07</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4533817.4</v>
+        <v>4584960.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3285624.1</t>
+          <t>3345198.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2558192.82</v>
+        <v>2500572.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1248193</t>
+          <t>1239762</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>207526.2403047743</t>
+          <t>228956.207707462</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>523546.3234615498</t>
+          <t>346821.0284222448</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-27.49</t>
+          <t>-28.92</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>183.67</t>
+          <t>178.701</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.07</v>
+        <v>23.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.63</v>
+        <v>23.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>167.29</t>
+          <t>356.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.01</t>
+          <t>-101.07</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4123414.6</v>
+        <v>4533817.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2993115.8</t>
+          <t>3285624.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2501026.3</v>
+        <v>2558192.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1130298</t>
+          <t>1248193</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>150068.0433671787</t>
+          <t>207526.2403047743</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>526542.4476797874</t>
+          <t>523546.3234615498</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-27.64</t>
+          <t>-27.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>226.67</t>
+          <t>183.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.31</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>24.01</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.95</v>
+        <v>23.07</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.62</v>
+        <v>23.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>167.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-102.01</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3544313</v>
+        <v>4123414.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2577512.1</t>
+          <t>2993115.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2550509.38</v>
+        <v>2501026.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>966800</t>
+          <t>1130298</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>81618.15167397709</t>
+          <t>150068.0433671787</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>490323.5734315636</t>
+          <t>526542.4476797874</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-27.64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>241.631</t>
+          <t>226.67</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-24.31</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>96.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.86</v>
+        <v>22.95</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.65</v>
+        <v>23.62</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3014163</v>
+        <v>3544313</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2221553.6</t>
+          <t>2577512.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2483633.94</v>
+        <v>2550509.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>966800</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7308.07499077954</t>
+          <t>81618.15167397709</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>316144.5897401171</t>
+          <t>490323.5734315636</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>241.631</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-25.69</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.77</v>
+        <v>22.86</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.68</v>
+        <v>23.65</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2105436.6</v>
+        <v>3014163</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1795643.8</t>
+          <t>2221553.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2426790.7</v>
+        <v>2483633.94</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-48844.01860000911</t>
+          <t>7308.07499077954</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>22121.87769018905</t>
+          <t>316144.5897401171</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-30.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>106.512</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.76</v>
+        <v>22.77</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.74</v>
+        <v>23.68</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.98</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2037430.8</v>
+        <v>2105436.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1798568.6</t>
+          <t>1795643.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2412719.42</v>
+        <v>2426790.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-61746.90883459059</t>
+          <t>-48844.01860000911</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>19992.97198707075</t>
+          <t>22121.87769018905</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-35.61</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,68 +3594,68 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.77</v>
+        <v>22.76</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.81</v>
+        <v>23.74</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1862817</v>
+        <v>2037430.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2395938.98</v>
+        <v>2412719.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-22072.46373120812</t>
+          <t>19992.97198707075</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,60 +4039,60 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.83</v>
+        <v>22.77</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.9</v>
+        <v>23.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1610711.2</v>
+        <v>1862817</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2389474.58</v>
+        <v>2395938.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-12697.2481954915</t>
+          <t>-22072.46373120812</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,17 +4469,17 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4489,33 +4489,33 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.91</v>
+        <v>22.83</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.98</v>
+        <v>23.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1428944.2</v>
+        <v>1610711.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2349514.76</v>
+        <v>2389474.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-130000.8599946292</t>
+          <t>-12697.2481954915</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.96</v>
+        <v>22.91</v>
       </c>
       <c r="AN11" t="n">
-        <v>24.05</v>
+        <v>23.98</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1485851</v>
+        <v>1428944.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2357132.54</v>
+        <v>2349514.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-124030.4889935888</t>
+          <t>-130000.8599946292</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>66.006</t>
+          <t>74.073</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-20.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-29.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.99</v>
+        <v>22.96</v>
       </c>
       <c r="AN12" t="n">
-        <v>24.11</v>
+        <v>24.05</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.19</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19501301.45922747</t>
+          <t>19478339.68928571</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1559706.4</v>
+        <v>1485851</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1953878.1</t>
+          <t>1868651.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2371167.86</v>
+        <v>2357132.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-394171</t>
+          <t>-382800</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-89111.03010474489</t>
+          <t>-94483.25454918241</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-142764.1558137604</t>
+          <t>-124030.4889935888</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1514150.0</t>
+          <t>1689629.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-34.05</t>
+          <t>-34.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.72</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>480.416</t>
+          <t>913.956</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-27.09</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.43</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
           <t>80.7</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.92999999999999</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>35.55</v>
+        <v>35.46</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.31</v>
+        <v>38.22</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-152.46</t>
+          <t>-149.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>21539363.8</v>
+        <v>21453226.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29791374.6</t>
+          <t>29423886.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>69388853.84</v>
+        <v>65660987.7</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-8252010</t>
+          <t>-7970659</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-5126877.888492357</t>
+          <t>-4943791.050532755</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-5162883.44207716</t>
+          <t>-3936813.441754945</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>579.265</t>
+          <t>480.416</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-21.69</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-13.43</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>35.68</v>
+        <v>35.55</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.41</v>
+        <v>38.31</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-153.33</t>
+          <t>-152.46</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>24319072.6</v>
+        <v>21539363.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>31053130.3</t>
+          <t>29791374.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>70329347.68000001</v>
+        <v>69388853.84</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-6734057</t>
+          <t>-8252010</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-5120331.424204211</t>
+          <t>-5126877.888492357</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-4981771.391034715</t>
+          <t>-5162883.44207716</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>494.417</t>
+          <t>579.265</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-21.69</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>33.76000000000001</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.51</v>
+        <v>38.41</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-13.17</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-152.87</t>
+          <t>-153.33</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>27292993</v>
+        <v>24319072.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31874128.5</t>
+          <t>31053130.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>72125013.59999999</v>
+        <v>70329347.68000001</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4581135</t>
+          <t>-6734057</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5145524.157507756</t>
+          <t>-5120331.424204211</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-4888185.339865692</t>
+          <t>-4981771.391034715</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>604.193</t>
+          <t>494.417</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>33.76000000000001</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>36.15</v>
+        <v>35.88</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.66</v>
+        <v>38.51</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-13.17</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-151.13</t>
+          <t>-152.87</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>32668185.6</v>
+        <v>27292993</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32630623.1</t>
+          <t>31874128.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>73222858.23999999</v>
+        <v>72125013.59999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>-4581135</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5192313.033442677</t>
+          <t>-5145524.157507756</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-4219103.468914736</t>
+          <t>-4888185.339865692</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1012.715</t>
+          <t>604.193</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>8.46</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>36.49</v>
+        <v>36.15</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.8</v>
+        <v>38.66</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-148.57</t>
+          <t>-151.13</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>37394546.6</v>
+        <v>32668185.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>33894957.9</t>
+          <t>32630623.1</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>74635589.06</v>
+        <v>73222858.23999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3499588</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5369260.226993212</t>
+          <t>-5192313.033442677</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3470619.815095</t>
+          <t>-4219103.468914736</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>893.111</t>
+          <t>1012.715</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,34 +7914,34 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>36.78</v>
+        <v>36.49</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.96</v>
+        <v>38.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-145.72</t>
+          <t>-148.57</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>38043385.4</v>
+        <v>37394546.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33628290.5</t>
+          <t>33894957.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>75765926.31999999</v>
+        <v>74635589.06</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4415094</t>
+          <t>3499588</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5714467.574611069</t>
+          <t>-5369260.226993212</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3731517.244813405</t>
+          <t>-3470619.815095</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>37.03</v>
+        <v>36.78</v>
       </c>
       <c r="AN19" t="n">
-        <v>39.1</v>
+        <v>38.96</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-143.27</t>
+          <t>-145.72</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>37787188</v>
+        <v>38043385.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>33357788.3</t>
+          <t>33628290.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>78618972.02</v>
+        <v>75765926.31999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>4429399</t>
+          <t>4415094</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6075003.998210644</t>
+          <t>-5714467.574611069</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3665692.349953502</t>
+          <t>-3731517.244813405</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>37.34</v>
+        <v>37.03</v>
       </c>
       <c r="AN20" t="n">
-        <v>39.24</v>
+        <v>39.1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>36455264</v>
+        <v>37787188</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>80453830.28</v>
+        <v>78618972.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3887846.987655312</t>
+          <t>-3665692.349953502</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,64 +9068,64 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-3.16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-4.59</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>37.58</v>
+        <v>37.34</v>
       </c>
       <c r="AN21" t="n">
-        <v>39.37</v>
+        <v>39.24</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>32593060.6</v>
+        <v>36455264</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>81339733.31999999</v>
+        <v>80453830.28</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-4991945.43481306</t>
+          <t>-3887846.987655312</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>37.74</v>
+        <v>37.58</v>
       </c>
       <c r="AN22" t="n">
-        <v>39.46</v>
+        <v>39.37</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>30395369.2</v>
+        <v>32593060.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>82590132.42</v>
+        <v>81339733.31999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-6401386.665223651</t>
+          <t>-4991945.43481306</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>812.259</t>
+          <t>1046.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-14.41</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>38</v>
+        <v>37.74</v>
       </c>
       <c r="AN23" t="n">
-        <v>39.57</v>
+        <v>39.46</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.03</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-20.30</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-134.40</t>
+          <t>-136.54</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>244228362.7521428</t>
+          <t>243951141.9179743</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>29213195.6</v>
+        <v>30395369.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>34657603.3</t>
+          <t>33994550.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>85238942.98</v>
+        <v>82590132.42</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-5444407</t>
+          <t>-3599181</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7526874.548620233</t>
+          <t>-7353722.566559221</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-7455976.792052239</t>
+          <t>-6401386.665223651</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>29564911.0</t>
+          <t>36939251.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>91.896</t>
+          <t>114.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.70</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>84.72</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>95.37</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.32</v>
+        <v>23.43</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.66</v>
+        <v>23.68</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2035.51</t>
+          <t>511.96</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-99.37</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2285375.0</t>
+          <t>2805376.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4584960.8</v>
+        <v>3958543</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3345198.7</t>
+          <t>3486353.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2500572.66</v>
+        <v>2484466.5</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1239762</t>
+          <t>472190</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>228956.207707462</t>
+          <t>232723.3867038795</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>346821.0284222448</t>
+          <t>253442.8711841754</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2285375.0</t>
+          <t>2805376.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-28.92</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>178.701</t>
+          <t>91.896</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-23.70</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.22</v>
+        <v>23.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.64</v>
+        <v>23.66</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>356.05</t>
+          <t>2035.51</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.07</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4533817.4</v>
+        <v>4584960.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3285624.1</t>
+          <t>3345198.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2558192.82</v>
+        <v>2500572.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1248193</t>
+          <t>1239762</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>207526.2403047743</t>
+          <t>228956.207707462</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>523546.3234615498</t>
+          <t>346821.0284222448</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-27.49</t>
+          <t>-28.92</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>183.67</t>
+          <t>178.701</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>23.07</v>
+        <v>23.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.63</v>
+        <v>23.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>167.29</t>
+          <t>356.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.01</t>
+          <t>-101.07</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4123414.6</v>
+        <v>4533817.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2993115.8</t>
+          <t>3285624.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2501026.3</v>
+        <v>2558192.82</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1130298</t>
+          <t>1248193</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>150068.0433671787</t>
+          <t>207526.2403047743</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>526542.4476797874</t>
+          <t>523546.3234615498</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-27.64</t>
+          <t>-27.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>226.67</t>
+          <t>183.67</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.31</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>96.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>24.01</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.95</v>
+        <v>23.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.62</v>
+        <v>23.63</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>167.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-102.01</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3544313</v>
+        <v>4123414.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2577512.1</t>
+          <t>2993115.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2550509.38</v>
+        <v>2501026.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>966800</t>
+          <t>1130298</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>81618.15167397709</t>
+          <t>150068.0433671787</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>490323.5734315636</t>
+          <t>526542.4476797874</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-27.64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>241.631</t>
+          <t>226.67</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-24.31</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>96.15</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.86</v>
+        <v>22.95</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.65</v>
+        <v>23.62</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3014163</v>
+        <v>3544313</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2221553.6</t>
+          <t>2577512.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2483633.94</v>
+        <v>2550509.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>966800</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7308.07499077954</t>
+          <t>81618.15167397709</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>316144.5897401171</t>
+          <t>490323.5734315636</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>241.631</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-25.69</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.77</v>
+        <v>22.86</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.68</v>
+        <v>23.65</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2105436.6</v>
+        <v>3014163</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1795643.8</t>
+          <t>2221553.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2426790.7</v>
+        <v>2483633.94</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-48844.01860000911</t>
+          <t>7308.07499077954</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>22121.87769018905</t>
+          <t>316144.5897401171</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-30.77</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>106.512</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.66</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.76</v>
+        <v>22.77</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.74</v>
+        <v>23.68</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.98</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2037430.8</v>
+        <v>2105436.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1798568.6</t>
+          <t>1795643.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2412719.42</v>
+        <v>2426790.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-61746.90883459059</t>
+          <t>-48844.01860000911</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>19992.97198707075</t>
+          <t>22121.87769018905</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-35.61</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,63 +4029,63 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.77</v>
+        <v>22.76</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.81</v>
+        <v>23.74</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1862817</v>
+        <v>2037430.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2395938.98</v>
+        <v>2412719.42</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-22072.46373120812</t>
+          <t>19992.97198707075</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,60 +4469,60 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.83</v>
+        <v>22.77</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.9</v>
+        <v>23.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1610711.2</v>
+        <v>1862817</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2389474.58</v>
+        <v>2395938.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-12697.2481954915</t>
+          <t>-22072.46373120812</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,17 +4899,17 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -4919,33 +4919,33 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.91</v>
+        <v>22.83</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.98</v>
+        <v>23.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1428944.2</v>
+        <v>1610711.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2349514.76</v>
+        <v>2389474.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-130000.8599946292</t>
+          <t>-12697.2481954915</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>74.073</t>
+          <t>62.525</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-19.64</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.97</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.96</v>
+        <v>22.91</v>
       </c>
       <c r="AN12" t="n">
-        <v>24.05</v>
+        <v>23.98</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19478339.68928571</t>
+          <t>19456556.12910128</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1485851</v>
+        <v>1428944.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1868651.0</t>
+          <t>1778210.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2357132.54</v>
+        <v>2349514.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-382800</t>
+          <t>-349265</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-94483.25454918241</t>
+          <t>-99947.50154078961</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-124030.4889935888</t>
+          <t>-130000.8599946292</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1689629.0</t>
+          <t>1393833.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-34.76</t>
+          <t>-36.61</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>913.956</t>
+          <t>703.435</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-27.09</t>
+          <t>-18.28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.97</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>87.85</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>34.92999999999999</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>35.46</v>
+        <v>35.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.22</v>
+        <v>38.08</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-149.86</t>
+          <t>-146.60</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>33264372.0</t>
+          <t>25702885.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>21453226.8</v>
+        <v>22569132</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29423886.7</t>
+          <t>27618658.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>65660987.7</v>
+        <v>62454970.46</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-7970659</t>
+          <t>-5049526</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-4943791.050532755</t>
+          <t>-4728939.447448566</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3936813.441754945</t>
+          <t>-3547255.63048552</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>33264372.0</t>
+          <t>25702885.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>480.416</t>
+          <t>913.956</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-27.09</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.43</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
           <t>80.7</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.92999999999999</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>35.55</v>
+        <v>35.46</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.31</v>
+        <v>38.22</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-152.46</t>
+          <t>-149.86</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>21539363.8</v>
+        <v>21453226.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>29791374.6</t>
+          <t>29423886.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>69388853.84</v>
+        <v>65660987.7</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-8252010</t>
+          <t>-7970659</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-5126877.888492357</t>
+          <t>-4943791.050532755</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-5162883.44207716</t>
+          <t>-3936813.441754945</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>579.265</t>
+          <t>480.416</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-21.69</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-13.43</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>35.68</v>
+        <v>35.55</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.41</v>
+        <v>38.31</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-153.33</t>
+          <t>-152.46</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>24319072.6</v>
+        <v>21539363.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31053130.3</t>
+          <t>29791374.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>70329347.68000001</v>
+        <v>69388853.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-6734057</t>
+          <t>-8252010</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5120331.424204211</t>
+          <t>-5126877.888492357</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-4981771.391034715</t>
+          <t>-5162883.44207716</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>494.417</t>
+          <t>579.265</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-21.69</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>33.76000000000001</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.51</v>
+        <v>38.41</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-13.17</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-152.87</t>
+          <t>-153.33</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>27292993</v>
+        <v>24319072.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>31874128.5</t>
+          <t>31053130.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>72125013.59999999</v>
+        <v>70329347.68000001</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-4581135</t>
+          <t>-6734057</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5145524.157507756</t>
+          <t>-5120331.424204211</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-4888185.339865692</t>
+          <t>-4981771.391034715</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>604.193</t>
+          <t>494.417</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>33.76000000000001</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>36.15</v>
+        <v>35.88</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.66</v>
+        <v>38.51</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-13.17</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-151.13</t>
+          <t>-152.87</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>32668185.6</v>
+        <v>27292993</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32630623.1</t>
+          <t>31874128.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>73222858.23999999</v>
+        <v>72125013.59999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>-4581135</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5192313.033442677</t>
+          <t>-5145524.157507756</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-4219103.468914736</t>
+          <t>-4888185.339865692</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1012.715</t>
+          <t>604.193</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>36.49</v>
+        <v>36.15</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.8</v>
+        <v>38.66</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-148.57</t>
+          <t>-151.13</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>37394546.6</v>
+        <v>32668185.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33894957.9</t>
+          <t>32630623.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>74635589.06</v>
+        <v>73222858.23999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3499588</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5369260.226993212</t>
+          <t>-5192313.033442677</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3470619.815095</t>
+          <t>-4219103.468914736</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>893.111</t>
+          <t>1012.715</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,34 +8344,34 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>36.78</v>
+        <v>36.49</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.96</v>
+        <v>38.8</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-145.72</t>
+          <t>-148.57</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>38043385.4</v>
+        <v>37394546.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>33628290.5</t>
+          <t>33894957.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>75765926.31999999</v>
+        <v>74635589.06</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>4415094</t>
+          <t>3499588</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5714467.574611069</t>
+          <t>-5369260.226993212</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3731517.244813405</t>
+          <t>-3470619.815095</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>37.03</v>
+        <v>36.78</v>
       </c>
       <c r="AN20" t="n">
-        <v>39.1</v>
+        <v>38.96</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-143.27</t>
+          <t>-145.72</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>37787188</v>
+        <v>38043385.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>33357788.3</t>
+          <t>33628290.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>78618972.02</v>
+        <v>75765926.31999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>4429399</t>
+          <t>4415094</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6075003.998210644</t>
+          <t>-5714467.574611069</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3665692.349953502</t>
+          <t>-3731517.244813405</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>37.34</v>
+        <v>37.03</v>
       </c>
       <c r="AN21" t="n">
-        <v>39.24</v>
+        <v>39.1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>36455264</v>
+        <v>37787188</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>80453830.28</v>
+        <v>78618972.02</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3887846.987655312</t>
+          <t>-3665692.349953502</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,64 +9498,64 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.99</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-3.16</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>37.58</v>
+        <v>37.34</v>
       </c>
       <c r="AN22" t="n">
-        <v>39.37</v>
+        <v>39.24</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>32593060.6</v>
+        <v>36455264</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>81339733.31999999</v>
+        <v>80453830.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-4991945.43481306</t>
+          <t>-3887846.987655312</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1046.8</t>
+          <t>1215.155</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-14.41</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>703</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.35</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>37.74</v>
+        <v>37.58</v>
       </c>
       <c r="AN23" t="n">
-        <v>39.46</v>
+        <v>39.37</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-136.54</t>
+          <t>-138.07</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>243951141.9179743</t>
+          <t>243658553.8632478</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>30395369.2</v>
+        <v>32593060.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>33994550.3</t>
+          <t>34295734.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>82590132.42</v>
+        <v>81339733.31999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3599181</t>
+          <t>-1702673</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-7353722.566559221</t>
+          <t>-6990372.238598272</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-6401386.665223651</t>
+          <t>-4991945.43481306</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>36939251.0</t>
+          <t>43755164.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>114.84</t>
+          <t>52.477</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>84.72</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.43</v>
+        <v>23.52</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.68</v>
+        <v>23.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.61</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>511.96</t>
+          <t>211.32</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.37</t>
+          <t>-98.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2805376.0</t>
+          <t>1300449.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3958543</v>
+        <v>3094428.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3486353.0</t>
+          <t>3319370.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2484466.5</v>
+        <v>2471199.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>472190</t>
+          <t>-224942</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>232723.3867038795</t>
+          <t>207515.5678783475</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>253442.8711841754</t>
+          <t>68872.5643379218</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2805376.0</t>
+          <t>1300449.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>91.896</t>
+          <t>114.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.70</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>84.72</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>95.37</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.32</v>
+        <v>23.43</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.66</v>
+        <v>23.68</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2035.51</t>
+          <t>511.96</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-99.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2285375.0</t>
+          <t>2805376.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4584960.8</v>
+        <v>3958543</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3345198.7</t>
+          <t>3486353.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2500572.66</v>
+        <v>2484466.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1239762</t>
+          <t>472190</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>228956.207707462</t>
+          <t>232723.3867038795</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>346821.0284222448</t>
+          <t>253442.8711841754</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2285375.0</t>
+          <t>2805376.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-28.92</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>178.701</t>
+          <t>91.896</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-23.70</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>23.22</v>
+        <v>23.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.64</v>
+        <v>23.66</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>356.05</t>
+          <t>2035.51</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.07</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4533817.4</v>
+        <v>4584960.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3285624.1</t>
+          <t>3345198.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2558192.82</v>
+        <v>2500572.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1248193</t>
+          <t>1239762</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>207526.2403047743</t>
+          <t>228956.207707462</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>523546.3234615498</t>
+          <t>346821.0284222448</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-27.49</t>
+          <t>-28.92</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>183.67</t>
+          <t>178.701</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>23.07</v>
+        <v>23.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.63</v>
+        <v>23.64</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>167.29</t>
+          <t>356.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.01</t>
+          <t>-101.07</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4123414.6</v>
+        <v>4533817.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2993115.8</t>
+          <t>3285624.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2501026.3</v>
+        <v>2558192.82</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1130298</t>
+          <t>1248193</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>150068.0433671787</t>
+          <t>207526.2403047743</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>526542.4476797874</t>
+          <t>523546.3234615498</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-27.64</t>
+          <t>-27.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>226.67</t>
+          <t>183.67</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.31</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>96.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>24.01</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.95</v>
+        <v>23.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.62</v>
+        <v>23.63</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>167.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-102.01</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3544313</v>
+        <v>4123414.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2577512.1</t>
+          <t>2993115.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2550509.38</v>
+        <v>2501026.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>966800</t>
+          <t>1130298</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>81618.15167397709</t>
+          <t>150068.0433671787</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>490323.5734315636</t>
+          <t>526542.4476797874</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-27.64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>241.631</t>
+          <t>226.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-24.31</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>96.15</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.86</v>
+        <v>22.95</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.65</v>
+        <v>23.62</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3014163</v>
+        <v>3544313</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2221553.6</t>
+          <t>2577512.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2483633.94</v>
+        <v>2550509.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>966800</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7308.07499077954</t>
+          <t>81618.15167397709</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>316144.5897401171</t>
+          <t>490323.5734315636</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>241.631</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-25.69</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.77</v>
+        <v>22.86</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.68</v>
+        <v>23.65</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2105436.6</v>
+        <v>3014163</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1795643.8</t>
+          <t>2221553.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2426790.7</v>
+        <v>2483633.94</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-48844.01860000911</t>
+          <t>7308.07499077954</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>22121.87769018905</t>
+          <t>316144.5897401171</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-30.77</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>106.512</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.76</v>
+        <v>22.77</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.74</v>
+        <v>23.68</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.98</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2037430.8</v>
+        <v>2105436.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1798568.6</t>
+          <t>1795643.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2412719.42</v>
+        <v>2426790.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-61746.90883459059</t>
+          <t>-48844.01860000911</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>19992.97198707075</t>
+          <t>22121.87769018905</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-35.61</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,68 +4454,68 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.77</v>
+        <v>22.76</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.81</v>
+        <v>23.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1862817</v>
+        <v>2037430.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2395938.98</v>
+        <v>2412719.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-22072.46373120812</t>
+          <t>19992.97198707075</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,60 +4899,60 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.83</v>
+        <v>22.77</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.9</v>
+        <v>23.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1610711.2</v>
+        <v>1862817</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2389474.58</v>
+        <v>2395938.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-12697.2481954915</t>
+          <t>-22072.46373120812</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>62.525</t>
+          <t>134.411</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.64</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-33.03</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,17 +5329,17 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5349,33 +5349,33 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.91</v>
+        <v>22.83</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.98</v>
+        <v>23.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.85</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19456556.12910128</t>
+          <t>19431618.97435898</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1428944.2</v>
+        <v>1610711.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1778210.1</t>
+          <t>1756518.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2349514.76</v>
+        <v>2389474.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-349265</t>
+          <t>-145807</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-99947.50154078961</t>
+          <t>-86524.38564151298</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-130000.8599946292</t>
+          <t>-12697.2481954915</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1393833.0</t>
+          <t>2970271.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-36.61</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.98</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>703.435</t>
+          <t>366.49</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.97</t>
+          <t>-12.45</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>87.85</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>35.78</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>35.36</v>
+        <v>35.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.08</v>
+        <v>37.98</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.41</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>32.10</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-146.60</t>
+          <t>-143.14</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>25702885.0</t>
+          <t>13189052.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>22569132</v>
+        <v>21850593</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27618658.8</t>
+          <t>24571793.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>62454970.46</v>
+        <v>55497823.04</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-5049526</t>
+          <t>-2721200</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-4728939.447448566</t>
+          <t>-4635936.647354137</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3547255.63048552</t>
+          <t>-4124421.246834781</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>25702885.0</t>
+          <t>13189052.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>913.956</t>
+          <t>703.435</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-27.09</t>
+          <t>-18.28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.97</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>87.85</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>34.92999999999999</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>35.46</v>
+        <v>35.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.22</v>
+        <v>38.08</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-149.86</t>
+          <t>-146.60</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33264372.0</t>
+          <t>25702885.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>21453226.8</v>
+        <v>22569132</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>29423886.7</t>
+          <t>27618658.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>65660987.7</v>
+        <v>62454970.46</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-7970659</t>
+          <t>-5049526</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-4943791.050532755</t>
+          <t>-4728939.447448566</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3936813.441754945</t>
+          <t>-3547255.63048552</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>33264372.0</t>
+          <t>25702885.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>480.416</t>
+          <t>913.956</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-27.09</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.43</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
           <t>80.7</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.92999999999999</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>35.55</v>
+        <v>35.46</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.31</v>
+        <v>38.22</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-152.46</t>
+          <t>-149.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>21539363.8</v>
+        <v>21453226.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>29791374.6</t>
+          <t>29423886.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>69388853.84</v>
+        <v>65660987.7</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-8252010</t>
+          <t>-7970659</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5126877.888492357</t>
+          <t>-4943791.050532755</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-5162883.44207716</t>
+          <t>-3936813.441754945</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>579.265</t>
+          <t>480.416</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-21.69</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-13.43</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>35.68</v>
+        <v>35.55</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.41</v>
+        <v>38.31</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-153.33</t>
+          <t>-152.46</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>24319072.6</v>
+        <v>21539363.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>31053130.3</t>
+          <t>29791374.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>70329347.68000001</v>
+        <v>69388853.84</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-6734057</t>
+          <t>-8252010</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5120331.424204211</t>
+          <t>-5126877.888492357</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-4981771.391034715</t>
+          <t>-5162883.44207716</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>494.417</t>
+          <t>579.265</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-21.69</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>33.76000000000001</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.51</v>
+        <v>38.41</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-13.17</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-152.87</t>
+          <t>-153.33</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>27292993</v>
+        <v>24319072.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>31874128.5</t>
+          <t>31053130.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>72125013.59999999</v>
+        <v>70329347.68000001</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-4581135</t>
+          <t>-6734057</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5145524.157507756</t>
+          <t>-5120331.424204211</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-4888185.339865692</t>
+          <t>-4981771.391034715</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>604.193</t>
+          <t>494.417</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>33.76000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>36.15</v>
+        <v>35.88</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.66</v>
+        <v>38.51</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-13.17</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-151.13</t>
+          <t>-152.87</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>32668185.6</v>
+        <v>27292993</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>32630623.1</t>
+          <t>31874128.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>73222858.23999999</v>
+        <v>72125013.59999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>-4581135</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5192313.033442677</t>
+          <t>-5145524.157507756</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-4219103.468914736</t>
+          <t>-4888185.339865692</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1012.715</t>
+          <t>604.193</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>36.49</v>
+        <v>36.15</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.8</v>
+        <v>38.66</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-148.57</t>
+          <t>-151.13</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>37394546.6</v>
+        <v>32668185.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>33894957.9</t>
+          <t>32630623.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>74635589.06</v>
+        <v>73222858.23999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>3499588</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5369260.226993212</t>
+          <t>-5192313.033442677</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3470619.815095</t>
+          <t>-4219103.468914736</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>893.111</t>
+          <t>1012.715</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,17 +8754,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,34 +8774,34 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>36.78</v>
+        <v>36.49</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.96</v>
+        <v>38.8</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-145.72</t>
+          <t>-148.57</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>38043385.4</v>
+        <v>37394546.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>33628290.5</t>
+          <t>33894957.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>75765926.31999999</v>
+        <v>74635589.06</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>4415094</t>
+          <t>3499588</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-5714467.574611069</t>
+          <t>-5369260.226993212</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3731517.244813405</t>
+          <t>-3470619.815095</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>37.03</v>
+        <v>36.78</v>
       </c>
       <c r="AN21" t="n">
-        <v>39.1</v>
+        <v>38.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-143.27</t>
+          <t>-145.72</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>37787188</v>
+        <v>38043385.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>33357788.3</t>
+          <t>33628290.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>78618972.02</v>
+        <v>75765926.31999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>4429399</t>
+          <t>4415094</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6075003.998210644</t>
+          <t>-5714467.574611069</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3665692.349953502</t>
+          <t>-3731517.244813405</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>37.34</v>
+        <v>37.03</v>
       </c>
       <c r="AN22" t="n">
-        <v>39.24</v>
+        <v>39.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>36455264</v>
+        <v>37787188</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>80453830.28</v>
+        <v>78618972.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-3887846.987655312</t>
+          <t>-3665692.349953502</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1215.155</t>
+          <t>1258.647</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,64 +9928,64 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-1.99</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-4.96</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-16.48</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>366</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>37.58</v>
+        <v>37.34</v>
       </c>
       <c r="AN23" t="n">
-        <v>39.37</v>
+        <v>39.24</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.12</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-138.07</t>
+          <t>-140.31</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>243658553.8632478</t>
+          <t>243340097.2830725</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>32593060.6</v>
+        <v>36455264</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>34295734.5</t>
+          <t>33847235.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>81339733.31999999</v>
+        <v>80453830.28</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1702673</t>
+          <t>2608028</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6990372.238598272</t>
+          <t>-6513060.661530125</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-4991945.43481306</t>
+          <t>-3887846.987655312</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>43755164.0</t>
+          <t>43657710.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>72.675</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>52.477</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.63</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.52</v>
+        <v>23.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.69</v>
+        <v>23.71</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>211.32</t>
+          <t>126.53</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-98.67</t>
+          <t>-98.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1300449.0</t>
+          <t>1813717.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3094428.6</v>
+        <v>2528830</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3319370.8</t>
+          <t>3326122.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2471199.48</v>
+        <v>2475691.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-224942</t>
+          <t>-797292</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>207515.5678783475</t>
+          <t>171966.5013489243</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>68872.5643379218</t>
+          <t>-23553.36456290353</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1300449.0</t>
+          <t>1813717.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-28.77</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>114.84</t>
+          <t>52.477</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>84.72</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.43</v>
+        <v>23.52</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.68</v>
+        <v>23.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.61</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>511.96</t>
+          <t>211.32</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.37</t>
+          <t>-98.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2805376.0</t>
+          <t>1300449.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3958543</v>
+        <v>3094428.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3486353.0</t>
+          <t>3319370.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2484466.5</v>
+        <v>2471199.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>472190</t>
+          <t>-224942</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>232723.3867038795</t>
+          <t>207515.5678783475</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>253442.8711841754</t>
+          <t>68872.5643379218</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2805376.0</t>
+          <t>1300449.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>91.896</t>
+          <t>114.84</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.70</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>84.72</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>95.37</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>23.32</v>
+        <v>23.43</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.66</v>
+        <v>23.68</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2035.51</t>
+          <t>511.96</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-99.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2285375.0</t>
+          <t>2805376.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4584960.8</v>
+        <v>3958543</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3345198.7</t>
+          <t>3486353.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2500572.66</v>
+        <v>2484466.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1239762</t>
+          <t>472190</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>228956.207707462</t>
+          <t>232723.3867038795</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>346821.0284222448</t>
+          <t>253442.8711841754</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2285375.0</t>
+          <t>2805376.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-28.92</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,42 +2173,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>91.896</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>178.701</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-2.21</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-23.70</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>23.22</v>
+        <v>23.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.64</v>
+        <v>23.66</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>356.05</t>
+          <t>2035.51</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.07</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4533817.4</v>
+        <v>4584960.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3285624.1</t>
+          <t>3345198.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2558192.82</v>
+        <v>2500572.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1248193</t>
+          <t>1239762</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>207526.2403047743</t>
+          <t>228956.207707462</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>523546.3234615498</t>
+          <t>346821.0284222448</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-27.49</t>
+          <t>-28.92</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>183.67</t>
+          <t>178.701</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>23.07</v>
+        <v>23.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.63</v>
+        <v>23.64</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>167.29</t>
+          <t>356.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.01</t>
+          <t>-101.07</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4123414.6</v>
+        <v>4533817.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2993115.8</t>
+          <t>3285624.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2501026.3</v>
+        <v>2558192.82</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1130298</t>
+          <t>1248193</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>150068.0433671787</t>
+          <t>207526.2403047743</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>526542.4476797874</t>
+          <t>523546.3234615498</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-27.64</t>
+          <t>-27.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>226.67</t>
+          <t>183.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.31</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>96.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>24.01</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.95</v>
+        <v>23.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.62</v>
+        <v>23.63</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>167.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-102.01</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3544313</v>
+        <v>4123414.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2577512.1</t>
+          <t>2993115.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2550509.38</v>
+        <v>2501026.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>966800</t>
+          <t>1130298</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>81618.15167397709</t>
+          <t>150068.0433671787</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>490323.5734315636</t>
+          <t>526542.4476797874</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-27.64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>241.631</t>
+          <t>226.67</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-24.31</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>96.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.86</v>
+        <v>22.95</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.65</v>
+        <v>23.62</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3014163</v>
+        <v>3544313</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2221553.6</t>
+          <t>2577512.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2483633.94</v>
+        <v>2550509.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>966800</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7308.07499077954</t>
+          <t>81618.15167397709</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>316144.5897401171</t>
+          <t>490323.5734315636</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>241.631</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-25.69</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.77</v>
+        <v>22.86</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.68</v>
+        <v>23.65</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2105436.6</v>
+        <v>3014163</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1795643.8</t>
+          <t>2221553.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2426790.7</v>
+        <v>2483633.94</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-48844.01860000911</t>
+          <t>7308.07499077954</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>22121.87769018905</t>
+          <t>316144.5897401171</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-30.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>106.512</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.66</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.76</v>
+        <v>22.77</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.74</v>
+        <v>23.68</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.98</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2037430.8</v>
+        <v>2105436.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1798568.6</t>
+          <t>1795643.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2412719.42</v>
+        <v>2426790.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-61746.90883459059</t>
+          <t>-48844.01860000911</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>19992.97198707075</t>
+          <t>22121.87769018905</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-35.61</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,68 +4884,68 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.77</v>
+        <v>22.76</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.81</v>
+        <v>23.74</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1862817</v>
+        <v>2037430.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2395938.98</v>
+        <v>2412719.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-22072.46373120812</t>
+          <t>19992.97198707075</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>134.411</t>
+          <t>80.828</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.03</t>
+          <t>-33.18</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,60 +5329,60 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.83</v>
+        <v>22.77</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.9</v>
+        <v>23.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.41</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>10.33</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.96</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19431618.97435898</t>
+          <t>19407847.93100996</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1610711.2</v>
+        <v>1862817</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1756518.5</t>
+          <t>1785043.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2389474.58</v>
+        <v>2395938.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-145807</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-86524.38564151298</t>
+          <t>-76608.70534761992</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-12697.2481954915</t>
+          <t>-22072.46373120812</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2970271.0</t>
+          <t>1746202.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-37.75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>79.98</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>366.49</t>
+          <t>397.518</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.45</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>81.43</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>80.48</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>35.78</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AM13" t="n">
         <v>35.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>37.98</v>
+        <v>37.85</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>32.10</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-143.14</t>
+          <t>-139.53</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>13189052.0</t>
+          <t>14328129.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>21850593</v>
+        <v>20686358.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>24571793.0</t>
+          <t>22502715.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>55497823.04</v>
+        <v>52244203.06</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2721200</t>
+          <t>-1816357</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-4635936.647354137</t>
+          <t>-4590391.912700946</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-4124421.246834781</t>
+          <t>-4339895.872108396</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>13189052.0</t>
+          <t>14328129.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>703.435</t>
+          <t>366.49</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.97</t>
+          <t>-12.45</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>87.85</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>35.78</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>35.36</v>
+        <v>35.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.08</v>
+        <v>37.98</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.41</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>32.10</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-146.60</t>
+          <t>-143.14</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>25702885.0</t>
+          <t>13189052.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>22569132</v>
+        <v>21850593</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>27618658.8</t>
+          <t>24571793.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>62454970.46</v>
+        <v>55497823.04</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-5049526</t>
+          <t>-2721200</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-4728939.447448566</t>
+          <t>-4635936.647354137</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3547255.63048552</t>
+          <t>-4124421.246834781</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>25702885.0</t>
+          <t>13189052.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>913.956</t>
+          <t>703.435</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-27.09</t>
+          <t>-18.28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.97</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>87.85</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>34.92999999999999</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>35.46</v>
+        <v>35.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.22</v>
+        <v>38.08</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-149.86</t>
+          <t>-146.60</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33264372.0</t>
+          <t>25702885.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>21453226.8</v>
+        <v>22569132</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>29423886.7</t>
+          <t>27618658.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>65660987.7</v>
+        <v>62454970.46</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-7970659</t>
+          <t>-5049526</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-4943791.050532755</t>
+          <t>-4728939.447448566</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3936813.441754945</t>
+          <t>-3547255.63048552</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>33264372.0</t>
+          <t>25702885.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>480.416</t>
+          <t>913.956</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-27.09</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-13.43</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
           <t>80.7</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.92999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>35.55</v>
+        <v>35.46</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.31</v>
+        <v>38.22</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-152.46</t>
+          <t>-149.86</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>21539363.8</v>
+        <v>21453226.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>29791374.6</t>
+          <t>29423886.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>69388853.84</v>
+        <v>65660987.7</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-8252010</t>
+          <t>-7970659</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5126877.888492357</t>
+          <t>-4943791.050532755</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-5162883.44207716</t>
+          <t>-3936813.441754945</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>579.265</t>
+          <t>480.416</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-21.69</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-13.43</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>35.68</v>
+        <v>35.55</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.41</v>
+        <v>38.31</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-153.33</t>
+          <t>-152.46</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>24319072.6</v>
+        <v>21539363.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>31053130.3</t>
+          <t>29791374.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>70329347.68000001</v>
+        <v>69388853.84</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-6734057</t>
+          <t>-8252010</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5120331.424204211</t>
+          <t>-5126877.888492357</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-4981771.391034715</t>
+          <t>-5162883.44207716</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>494.417</t>
+          <t>579.265</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-21.69</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>33.76000000000001</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.51</v>
+        <v>38.41</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-13.17</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-152.87</t>
+          <t>-153.33</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>27292993</v>
+        <v>24319072.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>31874128.5</t>
+          <t>31053130.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>72125013.59999999</v>
+        <v>70329347.68000001</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-4581135</t>
+          <t>-6734057</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5145524.157507756</t>
+          <t>-5120331.424204211</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-4888185.339865692</t>
+          <t>-4981771.391034715</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>604.193</t>
+          <t>494.417</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>33.76000000000001</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>36.15</v>
+        <v>35.88</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.66</v>
+        <v>38.51</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-13.17</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-151.13</t>
+          <t>-152.87</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>32668185.6</v>
+        <v>27292993</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>32630623.1</t>
+          <t>31874128.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>73222858.23999999</v>
+        <v>72125013.59999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>-4581135</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5192313.033442677</t>
+          <t>-5145524.157507756</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-4219103.468914736</t>
+          <t>-4888185.339865692</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1012.715</t>
+          <t>604.193</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>36.49</v>
+        <v>36.15</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.8</v>
+        <v>38.66</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-148.57</t>
+          <t>-151.13</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>37394546.6</v>
+        <v>32668185.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>33894957.9</t>
+          <t>32630623.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>74635589.06</v>
+        <v>73222858.23999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3499588</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-5369260.226993212</t>
+          <t>-5192313.033442677</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3470619.815095</t>
+          <t>-4219103.468914736</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>893.111</t>
+          <t>1012.715</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,17 +9184,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,34 +9204,34 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>36.78</v>
+        <v>36.49</v>
       </c>
       <c r="AN21" t="n">
-        <v>38.96</v>
+        <v>38.8</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-145.72</t>
+          <t>-148.57</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>38043385.4</v>
+        <v>37394546.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>33628290.5</t>
+          <t>33894957.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>75765926.31999999</v>
+        <v>74635589.06</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>4415094</t>
+          <t>3499588</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-5714467.574611069</t>
+          <t>-5369260.226993212</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3731517.244813405</t>
+          <t>-3470619.815095</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>37.03</v>
+        <v>36.78</v>
       </c>
       <c r="AN22" t="n">
-        <v>39.1</v>
+        <v>38.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-143.27</t>
+          <t>-145.72</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>37787188</v>
+        <v>38043385.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>33357788.3</t>
+          <t>33628290.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>78618972.02</v>
+        <v>75765926.31999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>4429399</t>
+          <t>4415094</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6075003.998210644</t>
+          <t>-5714467.574611069</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-3665692.349953502</t>
+          <t>-3731517.244813405</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>35018904.0</t>
+          <t>30845898.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1258.647</t>
+          <t>1034.778</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-18.19</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>37.34</v>
+        <v>37.03</v>
       </c>
       <c r="AN23" t="n">
-        <v>39.24</v>
+        <v>39.1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-140.31</t>
+          <t>-143.27</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>243340097.2830725</t>
+          <t>243024972.4197443</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>36455264</v>
+        <v>37787188</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>33847235.2</t>
+          <t>33357788.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>80453830.28</v>
+        <v>78618972.02</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2608028</t>
+          <t>4429399</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6513060.661530125</t>
+          <t>-6075003.998210644</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-3887846.987655312</t>
+          <t>-3665692.349953502</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>43657710.0</t>
+          <t>35018904.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/光罩.xlsx
+++ b/Result/checksun_type/光罩.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>72.675</t>
+          <t>36.686</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-42.61</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-23.70</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>81.63</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.62</v>
+        <v>23.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.71</v>
+        <v>23.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>126.53</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-98.06</t>
+          <t>-97.55</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1813717.0</t>
+          <t>917726.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2528830</v>
+        <v>1824528.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3326122.3</t>
+          <t>3179173.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2475691.88</v>
+        <v>2444952.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-797292</t>
+          <t>-1354644</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>171966.5013489243</t>
+          <t>121685.1925753346</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-23553.36456290353</t>
+          <t>-154862.0056794086</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1813717.0</t>
+          <t>917726.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-28.77</t>
+          <t>-28.92</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.477</t>
+          <t>72.675</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.63</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.52</v>
+        <v>23.62</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.69</v>
+        <v>23.71</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>211.32</t>
+          <t>126.53</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-98.67</t>
+          <t>-98.06</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1300449.0</t>
+          <t>1813717.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3094428.6</v>
+        <v>2528830</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3319370.8</t>
+          <t>3326122.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2471199.48</v>
+        <v>2475691.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-224942</t>
+          <t>-797292</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>207515.5678783475</t>
+          <t>171966.5013489243</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>68872.5643379218</t>
+          <t>-23553.36456290353</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1300449.0</t>
+          <t>1813717.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-28.77</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>114.84</t>
+          <t>52.477</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>84.72</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>83.85</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>23.43</v>
+        <v>23.52</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.68</v>
+        <v>23.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.61</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>511.96</t>
+          <t>211.32</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-99.37</t>
+          <t>-98.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2805376.0</t>
+          <t>1300449.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3958543</v>
+        <v>3094428.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3486353.0</t>
+          <t>3319370.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2484466.5</v>
+        <v>2471199.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>472190</t>
+          <t>-224942</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>232723.3867038795</t>
+          <t>207515.5678783475</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>253442.8711841754</t>
+          <t>68872.5643379218</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2805376.0</t>
+          <t>1300449.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>91.896</t>
+          <t>114.84</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.70</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>84.72</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>95.37</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>23.32</v>
+        <v>23.43</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.66</v>
+        <v>23.68</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2035.51</t>
+          <t>511.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.18</t>
+          <t>-99.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2285375.0</t>
+          <t>2805376.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4584960.8</v>
+        <v>3958543</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3345198.7</t>
+          <t>3486353.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2500572.66</v>
+        <v>2484466.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1239762</t>
+          <t>472190</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>228956.207707462</t>
+          <t>232723.3867038795</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>346821.0284222448</t>
+          <t>253442.8711841754</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2285375.0</t>
+          <t>2805376.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-28.92</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>178.701</t>
+          <t>91.896</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-23.70</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.58</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>23.22</v>
+        <v>23.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.64</v>
+        <v>23.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>356.05</t>
+          <t>2035.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.07</t>
+          <t>-100.18</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4533817.4</v>
+        <v>4584960.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3285624.1</t>
+          <t>3345198.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2558192.82</v>
+        <v>2500572.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1248193</t>
+          <t>1239762</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>207526.2403047743</t>
+          <t>228956.207707462</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>523546.3234615498</t>
+          <t>346821.0284222448</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4439233.0</t>
+          <t>2285375.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-27.49</t>
+          <t>-28.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>183.67</t>
+          <t>178.701</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-22.32</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.01</t>
+          <t>24.58</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>23.07</v>
+        <v>23.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.63</v>
+        <v>23.64</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>167.29</t>
+          <t>356.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.01</t>
+          <t>-101.07</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4123414.6</v>
+        <v>4533817.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2993115.8</t>
+          <t>3285624.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2501026.3</v>
+        <v>2558192.82</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1130298</t>
+          <t>1248193</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>150068.0433671787</t>
+          <t>207526.2403047743</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>526542.4476797874</t>
+          <t>523546.3234615498</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4641710.0</t>
+          <t>4439233.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-27.64</t>
+          <t>-27.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>226.67</t>
+          <t>183.67</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.31</t>
+          <t>-22.32</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>96.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>24.01</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.95</v>
+        <v>23.07</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.62</v>
+        <v>23.63</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>167.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-102.01</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3544313</v>
+        <v>4123414.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2577512.1</t>
+          <t>2993115.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2550509.38</v>
+        <v>2501026.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>966800</t>
+          <t>1130298</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>81618.15167397709</t>
+          <t>150068.0433671787</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>490323.5734315636</t>
+          <t>526542.4476797874</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5621021.0</t>
+          <t>4641710.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-27.64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>241.631</t>
+          <t>226.67</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>35.68</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-24.31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>96.15</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.86</v>
+        <v>22.95</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.65</v>
+        <v>23.62</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3014163</v>
+        <v>3544313</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2221553.6</t>
+          <t>2577512.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2483633.94</v>
+        <v>2550509.38</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>966800</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>7308.07499077954</t>
+          <t>81618.15167397709</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>316144.5897401171</t>
+          <t>490323.5734315636</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5937465.0</t>
+          <t>5621021.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>241.631</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>35.68</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.66</t>
+          <t>-25.69</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.77</v>
+        <v>22.86</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.68</v>
+        <v>23.65</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.87</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2105436.6</v>
+        <v>3014163</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1795643.8</t>
+          <t>2221553.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2426790.7</v>
+        <v>2483633.94</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>309792</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-48844.01860000911</t>
+          <t>7308.07499077954</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>22121.87769018905</t>
+          <t>316144.5897401171</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2029658.0</t>
+          <t>5937465.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-34.47</t>
+          <t>-30.77</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>106.512</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-30.89</t>
+          <t>-29.66</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.76</v>
+        <v>22.77</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.74</v>
+        <v>23.68</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.98</t>
+          <t>-103.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2037430.8</v>
+        <v>2105436.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1798568.6</t>
+          <t>1795643.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2412719.42</v>
+        <v>2426790.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-61746.90883459059</t>
+          <t>-48844.01860000911</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>19992.97198707075</t>
+          <t>22121.87769018905</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2387219.0</t>
+          <t>2029658.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-35.61</t>
+          <t>-34.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>80.828</t>
+          <t>106.512</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-33.18</t>
+          <t>-30.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,63 +5319,63 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.77</v>
+        <v>22.76</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.81</v>
+        <v>23.74</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.96</t>
+          <t>-103.98</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>19407847.93100996</t>
+          <t>19382235.34730114</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1862817</v>
+        <v>2037430.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1785043.4</t>
+          <t>1798568.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2395938.98</v>
+        <v>2412719.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-76608.70534761992</t>
+          <t>-61746.90883459059</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-22072.46373120812</t>
+          <t>19992.97198707075</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1746202.0</t>
+          <t>2387219.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-37.75</t>
+          <t>-35.61</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>397.518</t>
+          <t>411.252</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,64 +5628,64 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>35.9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-09-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-8.07</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-09-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>40.95</t>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.09</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,274 +5744,274 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>75.81</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>80.48</t>
+          <t>78.13</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>35.33</v>
+        <v>35.31</v>
       </c>
       <c r="AN13" t="n">
-        <v>37.85</v>
+        <v>37.74</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
+          <t>39.30</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-135.99</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>242711777.5531915</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>14815061.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>20259899.8</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>20899631.8</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>48774642.24</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-639732</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-4552748.666592681</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-4345710.812997222</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>14815061.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/07/22</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>14.33</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>光罩</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>光罩</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>2.372433013308771</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>-31.93695080052008</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>-18.77148256015754</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>7.11%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>-10.75%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>141.46</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>9100</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>光罩96.06%、其他3.94% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>光罩-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>半導體業右下上市</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
           <t>36.55</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-139.53</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>243024972.4197443</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>14328129.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>20686358.4</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>22502715.5</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>52244203.06</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-1816357</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-4590391.912700946</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-4339895.872108396</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>14328129.0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/07/22</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>光罩</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>光罩</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>2.372433013308771</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>-31.93695080052008</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>-18.77148256015754</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>5.24</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>7.11%</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>-10.75%</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>141.3</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>9125</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>光罩96.06%、其他3.94% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>光罩-半導體業-上市</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>半導體業右下上市</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>35.85</t>
-        </is>
-      </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>366.49</t>
+          <t>397.518</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-12.45</t>
+          <t>-12.09</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>81.43</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>80.48</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>35.78</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AM14" t="n">
         <v>35.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>37.98</v>
+        <v>37.85</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>32.10</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-143.14</t>
+          <t>-139.53</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>243024972.4197443</t>
+          <t>242711777.5531915</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>13189052.0</t>
+          <t>14328129.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>21850593</v>
+        <v>20686358.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>24571793.0</t>
+          <t>22502715.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>55497823.04</v>
+        <v>52244203.06</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2721200</t>
+          <t>-1816357</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-4635936.647354137</t>
+          <t>-4590391.912700946</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-4124421.246834781</t>
+          <t>-4339895.872108396</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>13189052.0</t>
+          <t>14328129.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.46</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>703.435</t>
+          <t>366.49</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.97</t>
+          <t>-12.45</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>87.85</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>35.78</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>35.36</v>
+        <v>35.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.08</v>
+        <v>37.98</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>38.41</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>32.10</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-146.60</t>
+          <t>-143.14</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>243024972.4197443</t>
+          <t>242711777.5531915</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>25702885.0</t>
+          <t>13189052.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>22569132</v>
+        <v>21850593</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>27618658.8</t>
+          <t>24571793.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>62454970.46</v>
+        <v>55497823.04</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-5049526</t>
+          <t>-2721200</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-4728939.447448566</t>
+          <t>-4635936.647354137</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3547255.63048552</t>
+          <t>-4124421.246834781</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>25702885.0</t>
+          <t>13189052.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.46</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>913.956</t>
+          <t>703.435</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-27.09</t>
+          <t>-18.28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-10.50</t>
+          <t>-11.97</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>87.85</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>34.92999999999999</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>35.46</v>
+        <v>35.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.22</v>
+        <v>38.08</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-149.86</t>
+          <t>-146.60</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>243024972.4197443</t>
+          <t>242711777.5531915</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>33264372.0</t>
+          <t>25702885.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>21453226.8</v>
+        <v>22569132</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>29423886.7</t>
+          <t>27618658.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>65660987.7</v>
+        <v>62454970.46</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-7970659</t>
+          <t>-5049526</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-4943791.050532755</t>
+          <t>-4728939.447448566</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3936813.441754945</t>
+          <t>-3547255.63048552</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>33264372.0</t>
+          <t>25702885.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.46</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>480.416</t>
+          <t>913.956</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-27.09</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-13.43</t>
+          <t>-10.50</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
           <t>80.7</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>58.1</t>
-        </is>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.92999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>35.55</v>
+        <v>35.46</v>
       </c>
       <c r="AN17" t="n">
-        <v>38.31</v>
+        <v>38.22</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-152.46</t>
+          <t>-149.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>243024972.4197443</t>
+          <t>242711777.5531915</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>21539363.8</v>
+        <v>21453226.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>29791374.6</t>
+          <t>29423886.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>69388853.84</v>
+        <v>65660987.7</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-8252010</t>
+          <t>-7970659</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5126877.888492357</t>
+          <t>-4943791.050532755</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-5162883.44207716</t>
+          <t>-3936813.441754945</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>16947354.0</t>
+          <t>33264372.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.46</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7753,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>579.265</t>
+          <t>480.416</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-21.69</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.77</t>
+          <t>-13.43</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>35.68</v>
+        <v>35.55</v>
       </c>
       <c r="AN18" t="n">
-        <v>38.41</v>
+        <v>38.31</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-153.33</t>
+          <t>-152.46</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>243024972.4197443</t>
+          <t>242711777.5531915</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>24319072.6</v>
+        <v>21539363.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>31053130.3</t>
+          <t>29791374.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>70329347.68000001</v>
+        <v>69388853.84</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-6734057</t>
+          <t>-8252010</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5120331.424204211</t>
+          <t>-5126877.888492357</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-4981771.391034715</t>
+          <t>-5162883.44207716</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>20149302.0</t>
+          <t>16947354.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.46</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>494.417</t>
+          <t>579.265</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-21.69</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>33.76000000000001</t>
+          <t>34.04</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.51</v>
+        <v>38.41</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-13.17</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-152.87</t>
+          <t>-153.33</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>243024972.4197443</t>
+          <t>242711777.5531915</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>27292993</v>
+        <v>24319072.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31874128.5</t>
+          <t>31053130.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>72125013.59999999</v>
+        <v>70329347.68000001</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-4581135</t>
+          <t>-6734057</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5145524.157507756</t>
+          <t>-5120331.424204211</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-4888185.339865692</t>
+          <t>-4981771.391034715</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>16781747.0</t>
+          <t>20149302.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.46</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>604.193</t>
+          <t>494.417</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>33.76000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>36.15</v>
+        <v>35.88</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.66</v>
+        <v>38.51</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-13.17</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-151.13</t>
+          <t>-152.87</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>243024972.4197443</t>
+          <t>242711777.5531915</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>32668185.6</v>
+        <v>27292993</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>32630623.1</t>
+          <t>31874128.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>73222858.23999999</v>
+        <v>72125013.59999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>-4581135</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-5192313.033442677</t>
+          <t>-5145524.157507756</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-4219103.468914736</t>
+          <t>-4888185.339865692</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>20123359.0</t>
+          <t>16781747.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.46</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1012.715</t>
+          <t>604.193</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>36.49</v>
+        <v>36.15</v>
       </c>
       <c r="AN21" t="n">
-        <v>38.8</v>
+        <v>38.66</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-23.45</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-148.57</t>
+          <t>-151.13</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>243024972.4197443</t>
+          <t>242711777.5531915</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>37394546.6</v>
+        <v>32668185.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>33894957.9</t>
+          <t>32630623.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>74635589.06</v>
+        <v>73222858.23999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3499588</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-5369260.226993212</t>
+          <t>-5192313.033442677</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3470619.815095</t>
+          <t>-4219103.468914736</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>33695057.0</t>
+          <t>20123359.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.46</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>893.111</t>
+          <t>1012.715</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,17 +9614,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>411</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9634,34 +9634,34 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>36.78</v>
+        <v>36.49</v>
       </c>
       <c r="AN22" t="n">
-        <v>38.96</v>
+        <v>38.8</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-23.45</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-145.72</t>
+          <t>-148.57</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>243024972.4197443</t>
+          <t>242711777.5531915</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>38043385.4</v>
+        <v>37394546.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>33628290.5</t>
+          <t>33894957.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>75765926.31999999</v>
+        <v>74635589.06</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>4415094</t>
+          <t>3499588</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-5714467.574611069</t>
+          <t>-5369260.226993212</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-3731517.244813405</t>
+          <t>-3470619.815095</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>30845898.0</t>
+          <t>33695057.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>141.46</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1034.778</t>
+          <t>893.111</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-18.19</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
      